--- a/csvpp_manual/CSVPP_TextFile_Generation_and_Processing.xlsx
+++ b/csvpp_manual/CSVPP_TextFile_Generation_and_Processing.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitwork\csvpp\csvpp_manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8771B73-1796-4AE3-AA51-DF9FA66C6C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1009E1-3A60-4BBF-BC84-B3EFBC4C89FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="165" yWindow="315" windowWidth="21285" windowHeight="14280" tabRatio="858" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
+    <workbookView xWindow="8700" yWindow="375" windowWidth="21285" windowHeight="14280" tabRatio="858" activeTab="4" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
   </bookViews>
   <sheets>
     <sheet name="テキストファイル生成" sheetId="28" r:id="rId1"/>
     <sheet name="テキストファイル加工" sheetId="29" r:id="rId2"/>
-    <sheet name="work" sheetId="30" r:id="rId3"/>
+    <sheet name="テキストファイル分割" sheetId="31" r:id="rId3"/>
+    <sheet name="CSVファイルセル内改行コード変換" sheetId="32" r:id="rId4"/>
+    <sheet name="CSVファイル横マージ" sheetId="33" r:id="rId5"/>
+    <sheet name="CSVファイル項目抽出" sheetId="34" r:id="rId6"/>
+    <sheet name="work" sheetId="30" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="437">
   <si>
     <t>[aa]</t>
   </si>
@@ -917,6 +921,553 @@
   <si>
     <t>7．まとめ</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>csv_textcut</t>
+  </si>
+  <si>
+    <t>csv_textcut</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分割元ファイル</t>
+  </si>
+  <si>
+    <t>c:\csv\in.csv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>c:\verilog\in.v</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>c:\verilog\netlist.v</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2．使用例</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#cut</t>
+  </si>
+  <si>
+    <t>c:\csv\out0</t>
+  </si>
+  <si>
+    <t>c:\csv\out1</t>
+  </si>
+  <si>
+    <t>c:\csv\out2</t>
+  </si>
+  <si>
+    <t>end</t>
+  </si>
+  <si>
+    <t>3．ルールファイルの構造</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  巨大なテキストファイルを 行番号で分割できる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  分割範囲は 開始行番号 ～ 終了行番号 で指定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  終了行番号に end を指定すると、ファイル末尾まで切り出し</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  出力ファイル名は フルパス指定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  複数の #cut を記述することで、複数ファイルへ分割可能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●動作説明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  netlist.v の 1～99 行 → out0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  100～199 行 → out1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  200～299 行 → out2</t>
+  </si>
+  <si>
+    <t>ルールファイルは #cut 命令のみで構成されます。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初めの行</t>
+  </si>
+  <si>
+    <t>　　1 行目を「1」として指定する</t>
+  </si>
+  <si>
+    <t>終わりの行</t>
+  </si>
+  <si>
+    <t>　　行番号を指定</t>
+  </si>
+  <si>
+    <t>　　ファイル末尾まで切り出したい場合は end を記述</t>
+  </si>
+  <si>
+    <t>出力ファイル名</t>
+  </si>
+  <si>
+    <t>　　必ず フルパスで指定する</t>
+  </si>
+  <si>
+    <t>　　同じファイル名を複数回指定すると、内容は追記される</t>
+  </si>
+  <si>
+    <t>c:\csv\out2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">  300 行～末尾 → out2（追記される）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4．まとめ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>csv_textcut は 行番号ベースのテキスト分割ツール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#cut の並びで複数の範囲を指定できる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>終了行に end を使うと末尾まで切り出し</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力ファイル名はフルパス必須</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>巨大なログ・ソースコード・設定ファイルの分割に便利</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>text_create / text_ctl と組み合わせると強力なテキスト加工環境になる</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVセル改行変換ツール（csvcellretchg / csvcellretchg2）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストファイル分割プログラム(csv_textcut)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1．csvcellretchg（複数ファイル一括変換）</t>
+  </si>
+  <si>
+    <t>このプログラムは コンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>CSV ファイル内の セル内改行を削除／置換するために使用します。</t>
+  </si>
+  <si>
+    <t>%exec</t>
+  </si>
+  <si>
+    <t>csvcellretchg</t>
+  </si>
+  <si>
+    <t>CSVファイル</t>
+  </si>
+  <si>
+    <t>[変換文字列]</t>
+  </si>
+  <si>
+    <t>[-dbl_no_cut]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  -dbl_no_cut</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">    不要なダブルコーテーションを削除しない。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●実行形式</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●使用例</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>c:\csv\*.csv</t>
+  </si>
+  <si>
+    <t>→ c:\csv 内のすべての .csv ファイルの セル内改行を削除</t>
+  </si>
+  <si>
+    <t>@@@@@</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ 改行を "@@@@@" に置換</t>
+  </si>
+  <si>
+    <t>こちらも コンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>csvcellretchg と異なり、入力ファイルと出力ファイルを明示的に指定します。</t>
+  </si>
+  <si>
+    <t>csvcellretchg2</t>
+  </si>
+  <si>
+    <t>csvcellretchg2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">変換前ファイル名 </t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変換後ファイル名</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●注意事項</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ファイル名は フルパス指定</t>
+  </si>
+  <si>
+    <t>標準入力／標準出力に対応</t>
+  </si>
+  <si>
+    <t>　変換前ファイル名に - を指定 → 標準入力</t>
+  </si>
+  <si>
+    <t>　変換後ファイル名に - を指定 → 標準出力</t>
+  </si>
+  <si>
+    <t>標準出力時の改行コードは 必ず 0x0d 0x0a（CRLF）</t>
+  </si>
+  <si>
+    <t>c:\csv\out.csv</t>
+  </si>
+  <si>
+    <t>c:\csv\out.csv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ 標準入力 → 標準出力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2．csvcellretchg2（単一ファイル変換）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3．まとめ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　複数 CSV ファイルをまとめて処理</t>
+  </si>
+  <si>
+    <t>　改行削除／置換が可能</t>
+  </si>
+  <si>
+    <t>　ワイルドカード対応</t>
+  </si>
+  <si>
+    <t>　入力ファイルと出力ファイルを明示的に指定</t>
+  </si>
+  <si>
+    <t>　標準入力／標準出力に対応</t>
+  </si>
+  <si>
+    <t>　改行コードは CRLF 固定</t>
+  </si>
+  <si>
+    <t>共通機能</t>
+  </si>
+  <si>
+    <t>　改行削除または任意文字列への置換</t>
+  </si>
+  <si>
+    <t>　バッファサイズ指定で高速化</t>
+  </si>
+  <si>
+    <t>　ダブルコーテーションの扱いを制御可能</t>
+  </si>
+  <si>
+    <t>aa0,bb1,cc2</t>
+  </si>
+  <si>
+    <t>aa1,bb2,cc3</t>
+  </si>
+  <si>
+    <t>aa2,bb3,cc4</t>
+  </si>
+  <si>
+    <t>dd4,ee5,ff6</t>
+  </si>
+  <si>
+    <t>dd5,ee6,ff7</t>
+  </si>
+  <si>
+    <t>dd6,ee7,ff8</t>
+  </si>
+  <si>
+    <t>dd7,ee8,ff9</t>
+  </si>
+  <si>
+    <t>aa0,bb1,cc2,dd4,ee5,ff6</t>
+  </si>
+  <si>
+    <t>aa1,bb2,cc3,dd5,ee6,ff7</t>
+  </si>
+  <si>
+    <t>aa2,bb3,cc4,dd6,ee7,ff8</t>
+  </si>
+  <si>
+    <t>,,,dd7,ee8,ff9</t>
+  </si>
+  <si>
+    <t>1．概要</t>
+  </si>
+  <si>
+    <t>csvmerge は複数の CSV ファイルを 横方向（列方向）に結合するコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>・行番号を基準に横方向へ結合</t>
+  </si>
+  <si>
+    <t>・行数が異なる場合は、存在しない行は空欄として扱う</t>
+  </si>
+  <si>
+    <t>・標準出力へ結果を出力する（リダイレクトでファイル保存）</t>
+  </si>
+  <si>
+    <t>2．使用方法</t>
+  </si>
+  <si>
+    <t>CSVファイル横マージ（csvmerge）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>csvmerge</t>
+  </si>
+  <si>
+    <t>CSVファイル1</t>
+  </si>
+  <si>
+    <t>CSVファイル2</t>
+  </si>
+  <si>
+    <t>CSVファイル3</t>
+  </si>
+  <si>
+    <t>&gt;</t>
+  </si>
+  <si>
+    <t>～</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVファイルn</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>※出力は必ずリダイレクトで指定する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3．使用例</t>
+  </si>
+  <si>
+    <t>3．使用例</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>%exec</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sample1.csv</t>
+  </si>
+  <si>
+    <t>sample2.csv</t>
+  </si>
+  <si>
+    <t>out.csv</t>
+  </si>
+  <si>
+    <t>&gt;</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>マージファイル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>入力ファイル例</t>
+  </si>
+  <si>
+    <t>[sample1.csv]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[sample2.csv]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[マージ結果（out.csv）]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●ポイント</t>
+  </si>
+  <si>
+    <t>sample1.csv は 3 行</t>
+  </si>
+  <si>
+    <t>sample2.csv は 4 行</t>
+  </si>
+  <si>
+    <t>行数が足りない場合は 空欄で埋める</t>
+  </si>
+  <si>
+    <t>CSVファイル項目抽出（csvcut）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>csvcut は CSV ファイルから 指定した列（項目）だけを抜き出すコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>・列番号は 1 から数える</t>
+  </si>
+  <si>
+    <t>・範囲指定（例：5-9）に対応</t>
+  </si>
+  <si>
+    <t>・標準入力／標準出力に対応</t>
+  </si>
+  <si>
+    <t>・抽出項目はカンマ区切りで指定</t>
+  </si>
+  <si>
+    <t>csvcut</t>
+  </si>
+  <si>
+    <t>入力CSVファイル</t>
+  </si>
+  <si>
+    <t>出力CSVファイル</t>
+  </si>
+  <si>
+    <t>抽出項目</t>
+  </si>
+  <si>
+    <t>●標準入力／標準出力</t>
+  </si>
+  <si>
+    <t>入力ファイル名に - を指定 → 標準入力</t>
+  </si>
+  <si>
+    <t>出力ファイル名に - を指定 → 標準出力</t>
+  </si>
+  <si>
+    <t>c:\csv\int.csv</t>
+  </si>
+  <si>
+    <t>1,5-9,11</t>
+  </si>
+  <si>
+    <t>→ 1列目、5〜9列目、11列目を抽出</t>
+  </si>
+  <si>
+    <t>●標準入力 → 標準出力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>|</t>
+  </si>
+  <si>
+    <t>記述</t>
+  </si>
+  <si>
+    <t>意味</t>
+  </si>
+  <si>
+    <t>1列目</t>
+  </si>
+  <si>
+    <t>5〜9列目</t>
+  </si>
+  <si>
+    <t>1列目、5〜9列目、11列目</t>
+  </si>
+  <si>
+    <t>5-9</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カンマ区切りで複数指定</t>
+  </si>
+  <si>
+    <t>範囲指定は - を使用</t>
+  </si>
+  <si>
+    <t>4．抽出項目の指定方法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定列だけを抽出</t>
+  </si>
+  <si>
+    <t>範囲指定に対応</t>
+  </si>
+  <si>
+    <t>標準入力／標準出力対応</t>
+  </si>
+  <si>
+    <t>列番号は 1 から数える</t>
+  </si>
+  <si>
+    <t>複数 CSV を横方向に結合</t>
+  </si>
+  <si>
+    <t>行数が足りない場合は空欄で補完</t>
+  </si>
+  <si>
+    <t>標準出力へ結果を出力</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1570,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1037,7 +1588,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2884,7 +3436,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD07EFE1-56C1-4F97-9C22-31B32909660F}">
-  <dimension ref="A1:H307"/>
+  <dimension ref="A1:H311"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
@@ -2926,13 +3478,13 @@
       <c r="E4" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="9" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3067,656 +3619,670 @@
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="B39" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B40" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="7"/>
+      <c r="B41" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="C41" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>115</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="D41" s="7"/>
       <c r="E41" s="7"/>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="7"/>
-      <c r="C42" s="7"/>
+      <c r="C42" s="7" t="s">
+        <v>199</v>
+      </c>
       <c r="D42" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>122</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="E42" s="7"/>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="7"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="7"/>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="7"/>
+      <c r="D44" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="7"/>
+      <c r="C45" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="7"/>
+      <c r="B46" s="7" t="s">
+        <v>124</v>
+      </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>123</v>
-      </c>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="7"/>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="C49" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="7"/>
+      <c r="C50" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D50" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="E49" s="7"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="7" t="s">
+      <c r="E50" s="7"/>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="5" t="s">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C52" s="7"/>
+      <c r="D52" s="7"/>
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="5" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="5" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="5" t="s">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="5" t="s">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="5" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="5" t="s">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="5" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="5" t="s">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="5" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="5" t="s">
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62" s="5" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="5" t="s">
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63" s="5" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B65" s="7" t="s">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B67" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="F67" s="8"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B68" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B66" s="7" t="s">
+      <c r="D68" s="7"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="7"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C69" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B67" s="7"/>
-      <c r="C67" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
-      <c r="D68" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="F68" s="7"/>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>123</v>
-      </c>
+      <c r="D69" s="7"/>
+      <c r="E69" s="7"/>
       <c r="F69" s="7"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B70" s="7"/>
       <c r="C70" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D70" s="7"/>
+        <v>199</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="E70" s="7"/>
       <c r="F70" s="7"/>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B71" s="7" t="s">
-        <v>124</v>
-      </c>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B71" s="7"/>
       <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
+      <c r="D71" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>122</v>
+      </c>
       <c r="F71" s="7"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B72" s="7"/>
       <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
+      <c r="D72" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="F72" s="7"/>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B73" s="7" t="s">
-        <v>118</v>
-      </c>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B73" s="7"/>
       <c r="C73" s="7" t="s">
-        <v>123</v>
+        <v>202</v>
       </c>
       <c r="D73" s="7"/>
       <c r="E73" s="7"/>
       <c r="F73" s="7"/>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B74" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>115</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C74" s="7"/>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
       <c r="F74" s="7"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B75" s="7"/>
-      <c r="C75" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>119</v>
-      </c>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
       <c r="E75" s="7"/>
       <c r="F75" s="7"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B76" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C76" s="7"/>
+        <v>118</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
       <c r="F76" s="7"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B77" s="7"/>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B77" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="C77" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>126</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D77" s="7"/>
       <c r="E77" s="7"/>
       <c r="F77" s="7"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B78" s="7"/>
-      <c r="C78" s="7"/>
+      <c r="C78" s="7" t="s">
+        <v>201</v>
+      </c>
       <c r="D78" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>126</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="E78" s="7"/>
       <c r="F78" s="7"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B79" s="7"/>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B79" s="7" t="s">
+        <v>125</v>
+      </c>
       <c r="C79" s="7"/>
-      <c r="D79" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>127</v>
-      </c>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
       <c r="F79" s="7"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B80" s="7"/>
       <c r="C80" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D80" s="7"/>
+        <v>204</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>126</v>
+      </c>
       <c r="E80" s="7"/>
       <c r="F80" s="7"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81" s="7"/>
-      <c r="C81" s="7" t="s">
-        <v>204</v>
-      </c>
+      <c r="C81" s="7"/>
       <c r="D81" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E81" s="7"/>
+        <v>200</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>126</v>
+      </c>
       <c r="F81" s="7"/>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" s="7"/>
       <c r="C82" s="7"/>
       <c r="D82" s="7" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F82" s="7"/>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="7"/>
-      <c r="C83" s="7"/>
-      <c r="D83" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>130</v>
-      </c>
+      <c r="C83" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
       <c r="F83" s="7"/>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84" s="7"/>
       <c r="C84" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D84" s="7"/>
+        <v>204</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>128</v>
+      </c>
       <c r="E84" s="7"/>
       <c r="F84" s="7"/>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85" s="7"/>
-      <c r="C85" s="7" t="s">
-        <v>204</v>
-      </c>
+      <c r="C85" s="7"/>
       <c r="D85" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="E85" s="7"/>
+        <v>200</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>129</v>
+      </c>
       <c r="F85" s="7"/>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86" s="7"/>
       <c r="C86" s="7"/>
       <c r="D86" s="7" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F86" s="7"/>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7" t="s">
-        <v>207</v>
-      </c>
+      <c r="C87" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D87" s="7"/>
       <c r="E87" s="7"/>
       <c r="F87" s="7"/>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88" s="7"/>
       <c r="C88" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D88" s="7"/>
+        <v>204</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="E88" s="7"/>
       <c r="F88" s="7"/>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89" s="7"/>
-      <c r="C89" s="7" t="s">
-        <v>204</v>
-      </c>
+      <c r="C89" s="7"/>
       <c r="D89" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E89" s="7"/>
+        <v>200</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>132</v>
+      </c>
       <c r="F89" s="7"/>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90" s="7"/>
       <c r="C90" s="7"/>
       <c r="D90" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>134</v>
-      </c>
+        <v>207</v>
+      </c>
+      <c r="E90" s="7"/>
       <c r="F90" s="7"/>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>135</v>
-      </c>
+      <c r="C91" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D91" s="7"/>
+      <c r="E91" s="7"/>
+      <c r="F91" s="7"/>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B92" s="7"/>
       <c r="C92" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D92" s="7"/>
+        <v>204</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>133</v>
+      </c>
       <c r="E92" s="7"/>
       <c r="F92" s="7"/>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B93" s="7" t="s">
-        <v>124</v>
-      </c>
+      <c r="B93" s="7"/>
       <c r="C93" s="7"/>
-      <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
+      <c r="D93" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>134</v>
+      </c>
       <c r="F93" s="7"/>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94" s="7"/>
       <c r="C94" s="7"/>
-      <c r="D94" s="7"/>
-      <c r="E94" s="7"/>
-      <c r="F94" s="7"/>
+      <c r="D94" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="95" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B95" s="7"/>
+      <c r="C95" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
+      <c r="F95" s="7"/>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C96" s="7"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="7"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B97" s="7"/>
+      <c r="C97" s="7"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B98" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C98" s="8"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="8"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B100" s="5" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B97" s="5" t="s">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B101" s="5" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B98" s="5" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B102" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B99" s="5" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B103" s="5" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B100" s="5" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B104" s="5" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="6" t="s">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="6" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B105" s="5" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B109" s="5" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B106" s="5" t="s">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B110" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B107" s="5" t="s">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B111" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B109" s="5" t="s">
+    <row r="113" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B113" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B110" s="7" t="s">
+    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B114" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="7" t="s">
+      <c r="C114" s="7" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B112" s="5" t="s">
+    <row r="116" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B116" s="5" t="s">
         <v>235</v>
-      </c>
-    </row>
-    <row r="114" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B114" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="115" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B115" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="118" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B118" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B119" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B122" s="5" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="120" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B120" s="5" t="s">
+    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B124" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="121" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B121" s="7" t="s">
+    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B125" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C121" s="7" t="s">
+      <c r="C125" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="D121" s="7" t="s">
+      <c r="D125" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E121" s="5" t="s">
+      <c r="E125" s="5" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="122" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B122" s="7" t="s">
+    <row r="126" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B126" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C122" s="7" t="s">
+      <c r="C126" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="D122" s="7" t="s">
+      <c r="D126" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="E122" s="5" t="s">
+      <c r="E126" s="5" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="123" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B123" s="7" t="s">
+    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B127" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7"/>
-      <c r="E123" s="5" t="s">
+      <c r="C127" s="7"/>
+      <c r="D127" s="7"/>
+      <c r="E127" s="5" t="s">
         <v>240</v>
-      </c>
-    </row>
-    <row r="124" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B124" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="125" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B125" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="C125" s="9"/>
-      <c r="D125" s="9"/>
-    </row>
-    <row r="127" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B127" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="128" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B128" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C128" s="7" t="s">
-        <v>121</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C128" s="7"/>
       <c r="D128" s="7"/>
+      <c r="E128" s="5" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B129" s="7"/>
-      <c r="C129" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D129" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B130" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7"/>
+      <c r="B129" s="5" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B131" s="7"/>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7"/>
+      <c r="B131" s="5" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="7" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D132" s="7"/>
     </row>
@@ -3726,47 +4292,45 @@
         <v>200</v>
       </c>
       <c r="D133" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C134" s="7"/>
       <c r="D134" s="7"/>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="7"/>
-      <c r="C135" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D135" s="7" t="s">
-        <v>144</v>
-      </c>
+      <c r="C135" s="7"/>
+      <c r="D135" s="7"/>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C136" s="7"/>
+        <v>139</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="D136" s="7"/>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="7"/>
-      <c r="C137" s="7"/>
-      <c r="D137" s="7"/>
+      <c r="C137" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D137" s="7" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="D138" s="7" t="s">
-        <v>145</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="C138" s="7"/>
+      <c r="D138" s="7"/>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="7"/>
@@ -3774,7 +4338,7 @@
         <v>200</v>
       </c>
       <c r="D139" s="7" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
@@ -3784,205 +4348,201 @@
       <c r="C140" s="7"/>
       <c r="D140" s="7"/>
     </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B141" s="7"/>
+      <c r="C141" s="7"/>
+      <c r="D141" s="7"/>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B142" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D142" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B143" s="5" t="s">
+      <c r="B143" s="7"/>
+      <c r="C143" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D143" s="7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B144" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C144" s="7"/>
+      <c r="D144" s="7"/>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B147" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="145" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B145" s="5" t="s">
+    <row r="149" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B149" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="146" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B146" s="7" t="s">
+    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B150" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C146" s="7" t="s">
+      <c r="C150" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D146" s="5" t="s">
+      <c r="D150" s="5" t="s">
         <v>243</v>
-      </c>
-    </row>
-    <row r="147" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B147" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C147" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D147" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="148" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B148" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="C148" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="150" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B150" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="151" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B151" s="7" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
+        <v>147</v>
+      </c>
+      <c r="D151" s="5" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="152" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B152" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C152" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B154" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B155" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C155" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D155" s="7"/>
+      <c r="E155" s="7"/>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B156" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="C152" s="7" t="s">
+      <c r="C156" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="D152" s="7"/>
-      <c r="E152" s="7"/>
-    </row>
-    <row r="153" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B153" s="7"/>
-      <c r="C153" s="7" t="s">
-        <v>199</v>
-      </c>
-      <c r="D153" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="E153" s="7"/>
-    </row>
-    <row r="154" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B154" s="7"/>
-      <c r="C154" s="7"/>
-      <c r="D154" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="155" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B155" s="7"/>
-      <c r="C155" s="7"/>
-      <c r="D155" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="E155" s="7" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="156" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B156" s="7"/>
-      <c r="C156" s="7" t="s">
-        <v>202</v>
       </c>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
     </row>
     <row r="157" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B157" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="C157" s="7"/>
-      <c r="D157" s="7"/>
+      <c r="B157" s="7"/>
+      <c r="C157" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="D157" s="7" t="s">
+        <v>115</v>
+      </c>
       <c r="E157" s="7"/>
     </row>
     <row r="158" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B158" s="7"/>
       <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
+      <c r="D158" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="159" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B159" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C159" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
+      <c r="B159" s="7"/>
+      <c r="C159" s="7"/>
+      <c r="D159" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="160" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B160" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="B160" s="7"/>
       <c r="C160" s="7" t="s">
-        <v>115</v>
+        <v>202</v>
       </c>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
     </row>
     <row r="161" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B161" s="7"/>
-      <c r="C161" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D161" s="7" t="s">
-        <v>150</v>
-      </c>
+      <c r="B161" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C161" s="7"/>
+      <c r="D161" s="7"/>
       <c r="E161" s="7"/>
     </row>
     <row r="162" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B162" s="7"/>
-      <c r="C162" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="D162" s="7" t="s">
-        <v>119</v>
-      </c>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
       <c r="E162" s="7"/>
     </row>
     <row r="163" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B163" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C163" s="7"/>
+        <v>118</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>123</v>
+      </c>
       <c r="D163" s="7"/>
       <c r="E163" s="7"/>
     </row>
     <row r="164" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B164" s="7"/>
+      <c r="B164" s="7" t="s">
+        <v>120</v>
+      </c>
       <c r="C164" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="D164" s="7" t="s">
-        <v>126</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="D164" s="7"/>
       <c r="E164" s="7"/>
     </row>
     <row r="165" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B165" s="7"/>
-      <c r="C165" s="7"/>
+      <c r="C165" s="7" t="s">
+        <v>210</v>
+      </c>
       <c r="D165" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="E165" s="7" t="s">
-        <v>126</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="E165" s="7"/>
     </row>
     <row r="166" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B166" s="7"/>
       <c r="C166" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D166" s="7"/>
+        <v>201</v>
+      </c>
+      <c r="D166" s="7" t="s">
+        <v>119</v>
+      </c>
       <c r="E166" s="7"/>
     </row>
     <row r="167" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B167" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C167" s="7"/>
       <c r="D167" s="7"/>
@@ -3990,83 +4550,92 @@
     </row>
     <row r="168" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B168" s="7"/>
-      <c r="C168" s="7"/>
-      <c r="D168" s="7"/>
+      <c r="C168" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="D168" s="7" t="s">
+        <v>126</v>
+      </c>
       <c r="E168" s="7"/>
     </row>
     <row r="169" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B169" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C169" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
+      <c r="D169" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="170" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B170" s="7" t="s">
-        <v>120</v>
-      </c>
+      <c r="B170" s="7"/>
       <c r="C170" s="7" t="s">
-        <v>151</v>
+        <v>202</v>
       </c>
       <c r="D170" s="7"/>
       <c r="E170" s="7"/>
     </row>
     <row r="171" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B171" s="7"/>
-      <c r="C171" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D171" s="7" t="s">
-        <v>152</v>
-      </c>
+      <c r="B171" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C171" s="7"/>
+      <c r="D171" s="7"/>
       <c r="E171" s="7"/>
     </row>
     <row r="172" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B172" s="7" t="s">
-        <v>124</v>
-      </c>
+      <c r="B172" s="7"/>
       <c r="C172" s="7"/>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
     </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B173" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C173" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D173" s="7"/>
+      <c r="E173" s="7"/>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B174" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C174" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D174" s="7"/>
+      <c r="E174" s="7"/>
+    </row>
     <row r="175" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B175" s="5" t="s">
+      <c r="B175" s="7"/>
+      <c r="C175" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D175" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E175" s="7"/>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B176" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C176" s="7"/>
+      <c r="D176" s="7"/>
+      <c r="E176" s="7"/>
+    </row>
+    <row r="179" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B179" s="5" t="s">
         <v>247</v>
-      </c>
-    </row>
-    <row r="177" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B177" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B178" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C178" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D178" s="5" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="179" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B179" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="C179" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B181" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
@@ -4074,7 +4643,10 @@
         <v>153</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>156</v>
+        <v>154</v>
+      </c>
+      <c r="D182" s="5" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
@@ -4082,112 +4654,112 @@
         <v>155</v>
       </c>
       <c r="C183" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D183" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B185" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B186" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C186" s="7" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="186" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B186" s="5" t="s">
+    <row r="187" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B187" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C187" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B190" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="188" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B188" s="5" t="s">
+    <row r="192" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B192" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="189" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B189" s="7" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="191" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B191" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="192" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B192" s="7" t="s">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B193" s="7" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="195" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B195" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B196" s="7" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B199" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B196" s="5" t="s">
+    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B200" s="5" t="s">
         <v>158</v>
-      </c>
-    </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B198" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B199" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C199" s="7" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B201" s="5" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="202" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B202" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="203" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B203" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C203" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B205" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="206" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B206" s="5" t="s">
         <v>253</v>
-      </c>
-    </row>
-    <row r="204" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B204" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="205" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B205" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="C205" s="7" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="208" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B208" s="5" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="210" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B210" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="211" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B211" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C211" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D211" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="E211" s="7" t="s">
-        <v>141</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B209" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C209" s="7" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="212" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B212" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="214" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B214" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="215" spans="2:5" x14ac:dyDescent="0.25">
@@ -4195,361 +4767,385 @@
         <v>162</v>
       </c>
       <c r="C215" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D215" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E215" s="7" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="216" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B216" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="218" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B218" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="219" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B219" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C219" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D215" s="7" t="s">
+      <c r="D219" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E215" s="7"/>
-    </row>
-    <row r="216" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B216" s="7" t="s">
+      <c r="E219" s="7"/>
+    </row>
+    <row r="220" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B220" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="C216" s="7" t="s">
+      <c r="C220" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D216" s="7" t="s">
+      <c r="D220" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="E216" s="7" t="s">
+      <c r="E220" s="7" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="219" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B219" s="5" t="s">
+    <row r="223" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B223" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="221" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B221" s="5" t="s">
+    <row r="225" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B225" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="222" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B222" s="7" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="224" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B224" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="225" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B225" s="7" t="s">
+    <row r="226" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B226" s="7" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="228" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B228" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="229" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B229" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="232" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B232" s="5" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="230" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B230" s="5" t="s">
+    <row r="234" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B234" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="231" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B231" s="7" t="s">
+    <row r="235" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B235" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C231" s="7" t="s">
+      <c r="C235" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="D231" s="7" t="s">
+      <c r="D235" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="E231" s="7" t="s">
+      <c r="E235" s="7" t="s">
         <v>173</v>
-      </c>
-    </row>
-    <row r="233" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B233" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="234" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B234" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C234" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D234" s="7" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="237" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B237" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="238" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B238" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C238" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D238" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="241" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B241" s="5" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="238" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B238" s="5" t="s">
+    <row r="242" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B242" s="5" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="240" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B240" s="5" t="s">
+    <row r="244" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B244" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="241" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B241" s="7" t="s">
+    <row r="245" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B245" s="7" t="s">
         <v>177</v>
       </c>
-      <c r="C241" s="7" t="s">
+      <c r="C245" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D241" s="7" t="s">
+      <c r="D245" s="7" t="s">
         <v>179</v>
-      </c>
-    </row>
-    <row r="243" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B243" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="244" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B244" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C244" s="7">
-        <v>3</v>
-      </c>
-      <c r="D244" s="7">
-        <v>4</v>
       </c>
     </row>
     <row r="247" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B247" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="248" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B248" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C248" s="7">
+        <v>3</v>
+      </c>
+      <c r="D248" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B251" s="5" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="248" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B248" s="5" t="s">
+    <row r="252" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B252" s="5" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="250" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B250" s="5" t="s">
+    <row r="254" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B254" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="251" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B251" s="7" t="s">
+    <row r="255" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B255" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C251" s="7" t="s">
+      <c r="C255" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="D251" s="7" t="s">
+      <c r="D255" s="7" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="253" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B253" s="5" t="s">
+    <row r="257" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B257" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="254" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B254" s="7" t="s">
+    <row r="258" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B258" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="C254" s="7">
+      <c r="C258" s="7">
         <v>100</v>
       </c>
-      <c r="D254" s="7" t="s">
+      <c r="D258" s="7" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="256" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B256" s="5" t="s">
+    <row r="260" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B260" s="5" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="257" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B257" s="5" t="s">
+    <row r="261" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B261" s="5" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="260" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B260" s="5" t="s">
+    <row r="264" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B264" s="5" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="261" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B261" s="5" t="s">
+    <row r="265" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B265" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="263" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B263" s="5" t="s">
+    <row r="267" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B267" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="264" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B264" s="7" t="s">
+    <row r="268" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B268" s="7" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="266" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B266" s="5" t="s">
+    <row r="270" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B270" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B267" s="7" t="s">
+    <row r="271" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B271" s="7" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="270" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B270" s="5" t="s">
+    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B274" s="5" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="271" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B271" s="5" t="s">
+    <row r="275" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B275" s="5" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="273" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B273" s="5" t="s">
+    <row r="277" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B277" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="274" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B274" s="7" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="276" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B276" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="277" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B277" s="7" t="s">
+    <row r="278" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B278" s="7" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="280" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B280" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="281" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B281" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="284" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B284" s="5" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="281" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B281" s="5" t="s">
+    <row r="285" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B285" s="5" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="283" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B283" s="5" t="s">
+    <row r="287" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B287" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="284" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B284" s="7" t="s">
+    <row r="288" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B288" s="7" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="286" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B286" s="5" t="s">
+    <row r="290" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B290" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B287" s="7" t="s">
+    <row r="291" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B291" s="7" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B290" s="5" t="s">
+    <row r="294" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B294" s="5" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B291" s="5" t="s">
+    <row r="295" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B295" s="5" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B293" s="5" t="s">
+    <row r="297" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B297" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B294" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="C294" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D294" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B295" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C295" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="D295" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B297" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B298" s="7" t="s">
         <v>195</v>
       </c>
       <c r="C298" s="7" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="299" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B299" s="7" t="s">
         <v>197</v>
       </c>
       <c r="C299" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D299" s="5" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="301" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B301" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="302" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B302" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C302" s="7" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A302" s="3" t="s">
+    <row r="303" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B303" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="C303" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A306" s="3" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B303" s="5" t="s">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B307" s="5" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B304" s="5" t="s">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B308" s="5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="305" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B305" s="5" t="s">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B309" s="5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="306" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B306" s="5" t="s">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B310" s="5" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="307" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B307" s="5" t="s">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B311" s="5" t="s">
         <v>265</v>
       </c>
     </row>
@@ -4562,6 +5158,1184 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83D69E0-543C-4B91-896D-469DD91AB079}">
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="19.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C22" s="7">
+        <v>1</v>
+      </c>
+      <c r="D22" s="7">
+        <v>99</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C23" s="7">
+        <v>100</v>
+      </c>
+      <c r="D23" s="7">
+        <v>199</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C24" s="7">
+        <v>200</v>
+      </c>
+      <c r="D24" s="7">
+        <v>299</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>280</v>
+      </c>
+      <c r="C25" s="7">
+        <v>300</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="5" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="5" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="5" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="5" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
+        <v>312</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FDB6C8-7508-4924-9487-D85D20963946}">
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="20" style="5" customWidth="1"/>
+    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="19.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B55" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B59" s="5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B60" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B61" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B62" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B64" s="5" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0813E8AE-00FC-4AD0-9277-F1CC2F47FD09}">
+  <dimension ref="A1:J44"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="6" width="12" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{677577AA-84BE-4292-B32A-990BC6D0E602}">
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="5"/>
+    <col min="7" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="3.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="7">
+        <v>1</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FBFDD87-441C-45E1-A53B-4B23BE47FAEB}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>

--- a/csvpp_manual/CSVPP_TextFile_Generation_and_Processing.xlsx
+++ b/csvpp_manual/CSVPP_TextFile_Generation_and_Processing.xlsx
@@ -8,18 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitwork\csvpp\csvpp_manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1009E1-3A60-4BBF-BC84-B3EFBC4C89FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB3AF84-2165-456B-8811-2D95F9097460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8700" yWindow="375" windowWidth="21285" windowHeight="14280" tabRatio="858" activeTab="4" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
+    <workbookView xWindow="-600" yWindow="1650" windowWidth="26205" windowHeight="14415" tabRatio="858" activeTab="7" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
   </bookViews>
   <sheets>
     <sheet name="テキストファイル生成" sheetId="28" r:id="rId1"/>
     <sheet name="テキストファイル加工" sheetId="29" r:id="rId2"/>
     <sheet name="テキストファイル分割" sheetId="31" r:id="rId3"/>
-    <sheet name="CSVファイルセル内改行コード変換" sheetId="32" r:id="rId4"/>
-    <sheet name="CSVファイル横マージ" sheetId="33" r:id="rId5"/>
-    <sheet name="CSVファイル項目抽出" sheetId="34" r:id="rId6"/>
-    <sheet name="work" sheetId="30" r:id="rId7"/>
+    <sheet name="テキストファイル連結・分割" sheetId="36" r:id="rId4"/>
+    <sheet name="LOG連結" sheetId="37" r:id="rId5"/>
+    <sheet name="改行コード変換" sheetId="38" r:id="rId6"/>
+    <sheet name="XML変換" sheetId="39" r:id="rId7"/>
+    <sheet name="SJIS-EUC変換" sheetId="40" r:id="rId8"/>
+    <sheet name="NULL変換" sheetId="41" r:id="rId9"/>
+    <sheet name="CSV-TAB変換" sheetId="42" r:id="rId10"/>
+    <sheet name="CSVファイルセル内改行コード変換" sheetId="32" r:id="rId11"/>
+    <sheet name="CSVファイル横マージ" sheetId="33" r:id="rId12"/>
+    <sheet name="CSVファイル項目抽出" sheetId="34" r:id="rId13"/>
+    <sheet name="work" sheetId="30" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,8 +45,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="877" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="735">
   <si>
     <t>[aa]</t>
   </si>
@@ -1071,10 +1100,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>テキストファイル分割プログラム(csv_textcut)</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>1．csvcellretchg（複数ファイル一括変換）</t>
   </si>
   <si>
@@ -1468,6 +1493,961 @@
   </si>
   <si>
     <t>標準出力へ結果を出力</t>
+  </si>
+  <si>
+    <t>-----------------------------------------------</t>
+  </si>
+  <si>
+    <t>１．ソフトの紹介</t>
+  </si>
+  <si>
+    <t>２．使用方法</t>
+  </si>
+  <si>
+    <t>本プログラムはコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>実行形式は以下の通りです。</t>
+  </si>
+  <si>
+    <t>例は以下の通りです。</t>
+  </si>
+  <si>
+    <t>ファイル名にワイルドカードが使用できます。</t>
+  </si>
+  <si>
+    <t>変換ファイル名はフルパスでお願いします。</t>
+  </si>
+  <si>
+    <t>#total_tag,DOC</t>
+  </si>
+  <si>
+    <t>#record_tag,REC</t>
+  </si>
+  <si>
+    <t>#tag,hinmei</t>
+  </si>
+  <si>
+    <t>#tag,tanka</t>
+  </si>
+  <si>
+    <t>#tag,suuryo</t>
+  </si>
+  <si>
+    <t>#total_tag,全体を定義するタグ名</t>
+  </si>
+  <si>
+    <t>#record_tag,レコード単位のタグ名</t>
+  </si>
+  <si>
+    <t>#tag,項目のタグ名</t>
+  </si>
+  <si>
+    <t>&lt;?xml version="1.0" encoding="Shift_JIS"?&gt;</t>
+  </si>
+  <si>
+    <t>&lt;?xml:stylesheet type="text/xsl" href="aaa.xsl"?&gt;</t>
+  </si>
+  <si>
+    <t>SJIS-EUC変換プログラム</t>
+  </si>
+  <si>
+    <t>本プログラムはＳＪＩＳコードとＥＵＣコードの相互変換するコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>eucsjis sjis_euc|euc_sjis 変換ファイル名</t>
+  </si>
+  <si>
+    <t>sjis_eucオプションでSJISからEUCに変換します。この時、改行コードは0x0aに変換します。</t>
+  </si>
+  <si>
+    <t>euc_sjisオプションでEUCからSJISに変換します。この時、改行コードは0x0d,0x0aに変換します。</t>
+  </si>
+  <si>
+    <t>オプションで改行コードを指定する時は</t>
+  </si>
+  <si>
+    <t>sjis_euc_win / euc_sjis_win は改行コードは0x0d,0x0aに変換します。</t>
+  </si>
+  <si>
+    <t>sjis_euc_unix / euc_sjis_unix は改行コードは0x0aに変換します。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eucsjis sjis_euc c:\csv\*.txt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">eucsjis euc_sjis c:\csv\*.txt </t>
+  </si>
+  <si>
+    <t>SJISコードの漢字で外字を使用する時はeucsjis.exeのあるディレクトリにeucsjis.csvファイルを置きます。</t>
+  </si>
+  <si>
+    <t>eucsjis.csvには変換則を記述します。添付のeucsjis.csvファイルは私(作者)が調査しましたSJISコードからEUCコードへの変換則です。</t>
+  </si>
+  <si>
+    <t>フォーマットは</t>
+  </si>
+  <si>
+    <t>#sjis_euc,1文字目のコード,2文字目のコード上限,2文字目のコード下限,1文字目のコード差分,2文字目のコード差分</t>
+  </si>
+  <si>
+    <t>#euc_sjis,1文字目のコード,2文字目のコード上限,2文字目のコード下限,1文字目のコード差分,2文字目のコード差分</t>
+  </si>
+  <si>
+    <t>#sjis_eucはsjisコードからeucコード変換の変換規則</t>
+  </si>
+  <si>
+    <t>#euc_sjisはeucコードからsjisコード変換の変換規則</t>
+  </si>
+  <si>
+    <t>以下は例です。</t>
+  </si>
+  <si>
+    <t>#sjis_euc,250,73,64,2,177</t>
+  </si>
+  <si>
+    <t>#sjis_euc,250,83,74,-77,107</t>
+  </si>
+  <si>
+    <t>eucsjis2 sjis_euc|euc_sjis 変換前ファイル名 変換後ファイル名</t>
+  </si>
+  <si>
+    <t>ファイル名はフルパスでお願いします。</t>
+  </si>
+  <si>
+    <t>また、変換前ファイル名に-を指定すると、標準入力になります。変換後ファイル名に-に指定すると標準出力になります。</t>
+  </si>
+  <si>
+    <t>標準出力の時の改行コードは必ず0x0d,0x0aになりますので注意してください。</t>
+  </si>
+  <si>
+    <t>eucsjis2 sjis_euc c:\csv\in.txt c:\csv\out.txt</t>
+  </si>
+  <si>
+    <t>type c:\csv\in.txt | eucsjis2 euc_sjis - - &gt; c:\csv\out.txt</t>
+  </si>
+  <si>
+    <t>NULL削除/置換プログラム</t>
+  </si>
+  <si>
+    <t>テキストファイル(特にCSVファイル)に混ざっているNULLを削除、または半角スペース、またはユニークコードに</t>
+  </si>
+  <si>
+    <t>変換するプログラムです。</t>
+  </si>
+  <si>
+    <t>nullchg 入力ファイル 出力ファイル [-chgsp] [-chg ユニークコード]  [-buff buffer_size]</t>
+  </si>
+  <si>
+    <t>-buff    :一回の読み書きに要する大きさ(単位はKByte)。通常は指定しませんが、ファイルが大きい時などには大きな値を指定すると有効です。指定しない場合は10KByteになっています。</t>
+  </si>
+  <si>
+    <t>※-chgsp、-chgの両方を指定しないときはNULLは削除されます。</t>
+  </si>
+  <si>
+    <t>nullchg.exe Sheet1.csv Sheet1.csv.del</t>
+  </si>
+  <si>
+    <t>nullchg.exe Sheet1.csv Sheet1.csv.sp -chgsp</t>
+  </si>
+  <si>
+    <t>nullchg.exe Sheet1.csv Sheet1.csv.uniq -chg [[NULL]]</t>
+  </si>
+  <si>
+    <t>TABファイル-&gt;CSVファイル変換プログラム</t>
+  </si>
+  <si>
+    <t>本プログラムはCSVMAKE2用フィルタとして作られています。</t>
+  </si>
+  <si>
+    <t>しかし、単体でも動作します。</t>
+  </si>
+  <si>
+    <t>変換内容はTABファイルをCSVファイルに変換します。</t>
+  </si>
+  <si>
+    <t>tabcsv TABファイル CSVファイル [-buff buffer_size] [-dbl_no_cut]</t>
+  </si>
+  <si>
+    <t>tabcsv c:\csv\bbb.txt c:\csv\ccc.csv</t>
+  </si>
+  <si>
+    <t>CSVMAKE2でフィルタプログラムとして使用する場合の例を以下に示します。</t>
+  </si>
+  <si>
+    <t>csvmake2 d:\aaa.xls -x tabcsv  c:\csv\bbb.txt c:\csv\ccc.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSVファイル-&gt;TABファイル変換プログラム </t>
+  </si>
+  <si>
+    <t>本プログラムはCSVMAKE用フィルタとして作られています。</t>
+  </si>
+  <si>
+    <t>変換内容はCSVファイルをTABファイルに変換します。</t>
+  </si>
+  <si>
+    <t>csvtab CSVファイル TABファイル [-buff buffer_size] [-dbl_no_cut]</t>
+  </si>
+  <si>
+    <t>csvtab c:\csv\bbb.csv c:\csv\ccc.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type c:\csv\bbb.csv | csvtab - - &gt; c:\csv\ccc.txt </t>
+  </si>
+  <si>
+    <t>※CSVファイル名を-にすると、標準入力になります。</t>
+  </si>
+  <si>
+    <t>※TABファイル名を-にすると、標準出力になります。</t>
+  </si>
+  <si>
+    <t>CSVMAKEでフィルタプログラムとして使用する場合の例を以下に示します。</t>
+  </si>
+  <si>
+    <t>csvmake d:\aaa.xls c:\csv csvtab txt</t>
+  </si>
+  <si>
+    <t>txt_catcut は、テキストファイルを 連結（追記） したり、</t>
+  </si>
+  <si>
+    <t>指定した行オフセット・サイズで 分割したりするためのコンソールプログラムです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・ファイル連結（append）</t>
+  </si>
+  <si>
+    <t>・ファイル新規作成（overwrite）</t>
+  </si>
+  <si>
+    <t>・行オフセット指定で読み出し位置を制御</t>
+  </si>
+  <si>
+    <t>・行数（size）指定で分割</t>
+  </si>
+  <si>
+    <t>・標準的なテキスト加工の前処理として便利</t>
+  </si>
+  <si>
+    <t>txt_catcut</t>
+  </si>
+  <si>
+    <t>in_file</t>
+  </si>
+  <si>
+    <t>out_file</t>
+  </si>
+  <si>
+    <t>[-new]</t>
+  </si>
+  <si>
+    <t>[-r_offset　offset]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[-w_offset offset]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[-size size]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプション</t>
+  </si>
+  <si>
+    <t>-new</t>
+  </si>
+  <si>
+    <t>出力ファイルを新規作成（既存内容を消す）</t>
+  </si>
+  <si>
+    <t>-r_offset offset</t>
+  </si>
+  <si>
+    <t>入力ファイルの読み出し開始行（1行目を1として数える）</t>
+  </si>
+  <si>
+    <t>-w_offset offset</t>
+  </si>
+  <si>
+    <t>出力ファイルの書き込み開始行（指定しない場合は末尾に追記）</t>
+  </si>
+  <si>
+    <t>-size size</t>
+  </si>
+  <si>
+    <t>読み書きする行数（指定しない場合は「入力ファイルの総行数 − r_offset」）</t>
+  </si>
+  <si>
+    <t>-buff buffer_size</t>
+  </si>
+  <si>
+    <t>読み書きバッファサイズ（KByte）。通常は指定不要（デフォルト：10KB）。大きなファイルで高速化したい場合に指定。</t>
+  </si>
+  <si>
+    <t>●数値指定の注意</t>
+  </si>
+  <si>
+    <t>行番号は 1 から数える</t>
+  </si>
+  <si>
+    <t>数値には 16進数が使用可能</t>
+  </si>
+  <si>
+    <t>　例：0x1000、0xa0df</t>
+  </si>
+  <si>
+    <t>3．動作仕様</t>
+  </si>
+  <si>
+    <t>→ out_file の末尾に in_file の内容がそのまま付加される</t>
+  </si>
+  <si>
+    <t>●オプションなしの場合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●-new を指定した場合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ out_file を新規作成し、in_file の内容を書き込む</t>
+  </si>
+  <si>
+    <t>●-r_offset を指定した場合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ in_file の 100行目から読み出す</t>
+  </si>
+  <si>
+    <t>●-w_offset を指定した場合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ out_file の 200行目から書き込む</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（既存内容がある場合はその位置から上書き）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●-size を指定した場合</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ in_file の読み出し開始位置から 100行分だけ書き込む</t>
+  </si>
+  <si>
+    <t>4．使用例</t>
+  </si>
+  <si>
+    <t>●動作</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>out.txt</t>
+  </si>
+  <si>
+    <t>in2.txt</t>
+  </si>
+  <si>
+    <t>in3.txt</t>
+  </si>
+  <si>
+    <t>out.txt を新規作成し、in1.txt を書き込む</t>
+  </si>
+  <si>
+    <t>in2.txt を out.txt の末尾に追記</t>
+  </si>
+  <si>
+    <t>in3.txt を out.txt の末尾に追記</t>
+  </si>
+  <si>
+    <t>(1).ファイル連結（append）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(2).100バイト単位で分割する例</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>out1.txt → in.txt の 1～100行</t>
+  </si>
+  <si>
+    <t>out2.txt → in.txt の 101～200行</t>
+  </si>
+  <si>
+    <t>out3.txt → in.txt の 201～300行</t>
+  </si>
+  <si>
+    <t>4．使用例</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>txt_catcut は テキストファイルの連結・分割専用ツール</t>
+  </si>
+  <si>
+    <t>行オフセット・書き込みオフセット・サイズ指定で柔軟に制御可能</t>
+  </si>
+  <si>
+    <t>バッファサイズ指定で大規模ファイルの高速処理が可能</t>
+  </si>
+  <si>
+    <t>16進数指定にも対応</t>
+  </si>
+  <si>
+    <t>ログ生成やテキスト加工の前処理として非常に便利</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -new で新規作成,指定なしで追記</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -new</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -r_offset</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -w_offset</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -size</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>in1.txt</t>
+  </si>
+  <si>
+    <t>in.txt</t>
+  </si>
+  <si>
+    <t>out1.txt</t>
+  </si>
+  <si>
+    <t>out2.txt</t>
+  </si>
+  <si>
+    <t>out3.txt</t>
+  </si>
+  <si>
+    <t>logcat</t>
+  </si>
+  <si>
+    <t>入力ファイル</t>
+  </si>
+  <si>
+    <t>出力ファイル</t>
+  </si>
+  <si>
+    <t>メッセージ</t>
+  </si>
+  <si>
+    <t>境界の行数</t>
+  </si>
+  <si>
+    <t>削減後行数</t>
+  </si>
+  <si>
+    <t>c:\csv\aaa.log</t>
+  </si>
+  <si>
+    <t>c:\csv\out.log</t>
+  </si>
+  <si>
+    <t>startting program</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -msg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -cut</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>はログファイルを</t>
+  </si>
+  <si>
+    <t>連結・メッセージ追加・行数制限による自動削減</t>
+  </si>
+  <si>
+    <t>を行うコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>主な用途：</t>
+  </si>
+  <si>
+    <t>・ログファイルへの追記</t>
+  </si>
+  <si>
+    <t>・ログファイルへのメッセージ追加</t>
+  </si>
+  <si>
+    <t>・ログファイルの行数が増えすぎた時の自動トリミング</t>
+  </si>
+  <si>
+    <t>ログローテーションの簡易版として使える便利なツールです。</t>
+  </si>
+  <si>
+    <t>3．機能説明</t>
+  </si>
+  <si>
+    <t>●ログ連結（通常モード）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出力ファイルが存在しない場合は新規作成される</t>
+  </si>
+  <si>
+    <t>入力ファイルの内容を 出力ファイルの末尾に追加する</t>
+  </si>
+  <si>
+    <t>●メッセージ追加（-msg）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定したメッセージを 出力ファイルの末尾に追加する</t>
+  </si>
+  <si>
+    <t>ログに簡易的なイベント記録を残す用途に便利</t>
+  </si>
+  <si>
+    <t>●行数制限によるログ削減（-cut）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve">出力ファイルの行数が 境界行数を超えた場合  </t>
+  </si>
+  <si>
+    <t>→ 先頭から行を削除し、行数が 削減後行数 になるまで削減する</t>
+  </si>
+  <si>
+    <t>用途</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ログファイルが肥大化するのを防ぐ</t>
+  </si>
+  <si>
+    <t>　常に最新のログだけを保持したい場合に便利</t>
+  </si>
+  <si>
+    <t>→ aaa.log の内容を out.log に追記</t>
+  </si>
+  <si>
+    <t>●ログ連結</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●メッセージ追加</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ out.log に「startting program」を追記</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●行数制限によるログ削減</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ out.log が 20,000行を超えたら、先頭から削除し、10,000行だけ残す</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>logcat はログ管理のための簡易ツール</t>
+  </si>
+  <si>
+    <t>入力ログの追記、メッセージ追加、行数制限による自動削減が可能</t>
+  </si>
+  <si>
+    <t>ログファイルの肥大化を防ぎ、最新ログだけを保持できる</t>
+  </si>
+  <si>
+    <t>CSVPP のバッチ処理や text_ctl と組み合わせると強力なログ管理環境になる</t>
+  </si>
+  <si>
+    <t>retchg</t>
+  </si>
+  <si>
+    <t>-m|-w|-u</t>
+  </si>
+  <si>
+    <t>c:\csv\*.txt</t>
+  </si>
+  <si>
+    <t>c:\csv\*.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -w</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -m</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -u</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -buff</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>対応する改行コード：</t>
+  </si>
+  <si>
+    <t>retchg はテキストファイルの 改行コードを変換するコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>OS</t>
+  </si>
+  <si>
+    <t>改行コード</t>
+  </si>
+  <si>
+    <t>Mac（旧OS）</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>-m</t>
+  </si>
+  <si>
+    <t>Windows</t>
+  </si>
+  <si>
+    <t>CRLF</t>
+  </si>
+  <si>
+    <t>-w</t>
+  </si>
+  <si>
+    <t>Unix / Linux</t>
+  </si>
+  <si>
+    <t>LF</t>
+  </si>
+  <si>
+    <t>-u</t>
+  </si>
+  <si>
+    <t>●パラメータ説明</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Mac 用改行コード（CR）に変換</t>
+  </si>
+  <si>
+    <t>Windows 用改行コード（CRLF）に変換</t>
+  </si>
+  <si>
+    <t>Unix 用改行コード（LF）に変換</t>
+  </si>
+  <si>
+    <t>注意事項</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・変換ファイル名はフルパスで指定すること</t>
+  </si>
+  <si>
+    <t>・ワイルドカード（*.txt など）が使用可能</t>
+  </si>
+  <si>
+    <t>・大規模ファイルを扱う場合は -buff を大きくすると高速化できる</t>
+  </si>
+  <si>
+    <t>●Windows 改行コード（CRLF）へ変換</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●Mac 改行コード（CR）へ変換</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●Unix 改行コード（LF）へ変換</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●バッファサイズを指定して高速化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・retchg は 改行コードの一括変換ツール</t>
+  </si>
+  <si>
+    <t>・Mac / Windows / Unix の改行コードに対応</t>
+  </si>
+  <si>
+    <t>・ワイルドカードで複数ファイルをまとめて変換可能</t>
+  </si>
+  <si>
+    <t>・大規模ファイルは -buff 指定で高速化</t>
+  </si>
+  <si>
+    <t>・CSVPP の前処理・後処理として非常に便利</t>
+  </si>
+  <si>
+    <t>csvxml</t>
+  </si>
+  <si>
+    <t>csv_file</t>
+  </si>
+  <si>
+    <t>xml_file</t>
+  </si>
+  <si>
+    <t>[-e]</t>
+  </si>
+  <si>
+    <t>[-tag タグ設定ファイル]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[-header ヘッダファイル]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[-buff サイズ]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>data.csv</t>
+  </si>
+  <si>
+    <t>data.xml</t>
+  </si>
+  <si>
+    <t>tag.csv</t>
+  </si>
+  <si>
+    <t>header.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -tag</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -header</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>主な特徴：</t>
+  </si>
+  <si>
+    <t>csvxml は CSV ファイルを XML 形式へ変換するコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>・CSV → XML の自動変換</t>
+  </si>
+  <si>
+    <t>・タグ設定ファイルで XML の構造を自由に定義可能</t>
+  </si>
+  <si>
+    <t>・ヘッダファイルで XML の先頭行を指定可能</t>
+  </si>
+  <si>
+    <t>・エスケープコード変換に対応（無効化も可能）</t>
+  </si>
+  <si>
+    <t>・大規模ファイルはバッファサイズ指定で高速化可能</t>
+  </si>
+  <si>
+    <t>-tag タグ設定ファイル</t>
+  </si>
+  <si>
+    <t>XML のタグ名を定義するファイルを指定</t>
+  </si>
+  <si>
+    <t>-header ヘッダファイル</t>
+  </si>
+  <si>
+    <t>XML の先頭行（ヘッダ）を指定</t>
+  </si>
+  <si>
+    <t>-buff サイズ</t>
+  </si>
+  <si>
+    <t>読み書きバッファサイズ（KByte）。通常は指定不要（デフォルト：10KB）</t>
+  </si>
+  <si>
+    <t>-e</t>
+  </si>
+  <si>
+    <t>エスケープコード変換を行わない</t>
+  </si>
+  <si>
+    <t>●オプション一覧</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タグ設定ファイルでは、XML の構造を以下の 3 種類のタグで定義します。</t>
+  </si>
+  <si>
+    <t>・全体タグ（total_tag）</t>
+  </si>
+  <si>
+    <t>・レコードタグ（record_tag）</t>
+  </si>
+  <si>
+    <t>・項目タグ（tag）</t>
+  </si>
+  <si>
+    <t>●CSV例（タグ設定ファイル）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●タグを指定しない場合のデフォルト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>種類</t>
+  </si>
+  <si>
+    <t>デフォルト値</t>
+  </si>
+  <si>
+    <t>全体タグ</t>
+  </si>
+  <si>
+    <t>DOC</t>
+  </si>
+  <si>
+    <t>レコードタグ</t>
+  </si>
+  <si>
+    <t>REC</t>
+  </si>
+  <si>
+    <t>項目タグ</t>
+  </si>
+  <si>
+    <t>TAG1, TAG2, TAG3 ...</t>
+  </si>
+  <si>
+    <t>3．タグ設定ファイル（tag.csv）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4．タグ設定ファイルの構造</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(1) 全体タグの指定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例：</t>
+  </si>
+  <si>
+    <t>(2) レコードタグの指定</t>
+  </si>
+  <si>
+    <t>(3) 項目タグの指定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>(4) エスケープコード変換</t>
+  </si>
+  <si>
+    <t>XML では以下の文字がエスケープされます：</t>
+  </si>
+  <si>
+    <t>文字</t>
+  </si>
+  <si>
+    <t>変換後</t>
+  </si>
+  <si>
+    <t>&amp;</t>
+  </si>
+  <si>
+    <t>&amp;amp;</t>
+  </si>
+  <si>
+    <t>&amp;gt;</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>&amp;lt;</t>
+  </si>
+  <si>
+    <t>"</t>
+  </si>
+  <si>
+    <t>&amp;quot;</t>
+  </si>
+  <si>
+    <t>'</t>
+  </si>
+  <si>
+    <t>&amp;apos;</t>
+  </si>
+  <si>
+    <t>※ -e オプションを指定すると 変換しない</t>
+  </si>
+  <si>
+    <t>4．ヘッダファイル</t>
+  </si>
+  <si>
+    <t>ヘッダファイルは XML の 1行目・2行目 を記述するためのファイルです。</t>
+  </si>
+  <si>
+    <t>使用例（header.txt）</t>
+  </si>
+  <si>
+    <t>XML の仕様に従って自由に記述できます。</t>
+  </si>
+  <si>
+    <t>csvxml は CSV → XML の変換ツール</t>
+  </si>
+  <si>
+    <t>タグ設定ファイルで XML の構造を柔軟に定義可能</t>
+  </si>
+  <si>
+    <t>・エスケープコード変換はデフォルト ON（-e で OFF）</t>
+  </si>
+  <si>
+    <t>・デフォルトタグは DOC / REC / TAG1～n</t>
+  </si>
+  <si>
+    <t>CSVPP の周辺ツールの中でも、</t>
+  </si>
+  <si>
+    <t>データ連携・外部システムとのインターフェース構築に非常に便利な機能です。</t>
+  </si>
+  <si>
+    <t>XML変換（csvxml）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>改行コード変換（retchg）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LOG連結（logcat）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストファイル連結・分割（txt_catcut）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストファイル分割(csv_textcut)</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1539,7 +2519,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1562,6 +2542,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1570,7 +2587,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1590,6 +2607,18 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -3434,6 +4463,1122 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE2CDF9-050B-4574-9296-ED6789081A87}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9" style="5"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="e" cm="1">
+        <f t="array" ref="B18">-dbl_no_cut :不要なダブルコーテーションを削除しない様にする。</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="5" t="e" cm="1">
+        <f t="array" ref="B45">-dbl_no_cut :不要なダブルコーテーションを削除しない様にする。</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="5" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="5" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="5" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="5" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="5" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FDB6C8-7508-4924-9487-D85D20963946}">
+  <dimension ref="A1:H72"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="20" style="5" customWidth="1"/>
+    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="19.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="2"/>
+      <c r="B18" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="2" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="2"/>
+      <c r="B48" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B55" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B59" s="5" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B60" s="5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B61" s="5" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B62" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B64" s="5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="5" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="5" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="5" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="5" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="5" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="5" t="s">
+        <v>358</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0813E8AE-00FC-4AD0-9277-F1CC2F47FD09}">
+  <dimension ref="A1:J44"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="6" width="12" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>388</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="5" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
+        <v>435</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{677577AA-84BE-4292-B32A-990BC6D0E602}">
+  <dimension ref="A1:K37"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="26.75" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="5"/>
+    <col min="7" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="3.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>408</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="H22" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="I22" s="9" t="s">
+        <v>415</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B27" s="7">
+        <v>1</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B28" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FBFDD87-441C-45E1-A53B-4B23BE47FAEB}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9" style="5"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD07EFE1-56C1-4F97-9C22-31B32909660F}">
   <dimension ref="A1:H311"/>
@@ -5173,7 +7318,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>734</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5465,390 +7610,575 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FDB6C8-7508-4924-9487-D85D20963946}">
-  <dimension ref="A1:H72"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DCBBDD-5C69-4CD5-80ED-D60C3A6CB84D}">
+  <dimension ref="A1:J77"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="1" max="1" width="3.25" style="6" customWidth="1"/>
     <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="20" style="5" customWidth="1"/>
-    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="15" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="19.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="27.75" style="5" customWidth="1"/>
+    <col min="4" max="4" width="7.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="G8" s="9" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="14"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>524</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="14"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B20" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="E22" s="10" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>529</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="14"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="2" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>321</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="G37" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B41" s="2" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B42" s="2" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B43" s="2" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B44" s="2" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B45" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B46" s="2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="2"/>
-      <c r="B48" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B50" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="G41" s="7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B43" s="5" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="G46" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B51" s="5" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" s="7" t="s">
-        <v>318</v>
+        <v>387</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>334</v>
+        <v>514</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>276</v>
+        <v>572</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B55" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B56" s="2" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B53" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="F53" s="7"/>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B54" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="F54" s="7"/>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B57" s="5" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B58" s="5" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" s="5" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B60" s="5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" s="5" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B62" s="5" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B64" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B62" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="H62" s="7">
+        <v>100</v>
+      </c>
+      <c r="I62" s="7"/>
+      <c r="J62" s="7"/>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B63" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="H63" s="7">
+        <v>100</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="J63" s="7">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>576</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="H64" s="7">
+        <v>100</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="J64" s="7">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B66" s="5" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B67" s="5" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="5" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B69" s="5" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71" s="5" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B72" s="5" t="s">
-        <v>359</v>
+        <v>562</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="5" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="5" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="5" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="5" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="5" t="s">
+        <v>566</v>
       </c>
     </row>
   </sheetData>
@@ -5860,24 +8190,22 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0813E8AE-00FC-4AD0-9277-F1CC2F47FD09}">
-  <dimension ref="A1:J44"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5C4333-F641-40BB-B2E3-89805723AF26}">
+  <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
-    <col min="4" max="6" width="12" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="2"/>
+    <col min="3" max="3" width="15.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>377</v>
+        <v>732</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -5885,208 +8213,367 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>588</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>589</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>378</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C13" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>378</v>
+        <v>577</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>389</v>
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>390</v>
+        <v>579</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+        <v>580</v>
+      </c>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="5" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="5" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B38" s="5" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B43" s="5" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B44" s="5" t="s">
-        <v>436</v>
+        <v>611</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="G45" s="7"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="5" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="5" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="F49" s="7">
+        <v>20000</v>
+      </c>
+      <c r="G49" s="7">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B50" s="5" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B54" s="5" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B55" s="5" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B57" s="5" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -6098,25 +8585,24 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{677577AA-84BE-4292-B32A-990BC6D0E602}">
-  <dimension ref="A1:K37"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E8EB3C0-1183-4B92-862F-140ADBEFBE28}">
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="26.75" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
     <col min="4" max="4" width="15" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="5"/>
-    <col min="7" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="3.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="18.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="19.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9" style="2"/>
+    <col min="9" max="9" width="17.625" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>402</v>
+        <v>731</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -6126,205 +8612,295 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>403</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>405</v>
+        <v>627</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>406</v>
+      <c r="B7" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>630</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>407</v>
+      <c r="B8" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>411</v>
+      <c r="B10" s="7" t="s">
+        <v>637</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>638</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>412</v>
+      <c r="A13" s="3" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="H22" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="J22" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="K22" s="9" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="7">
-        <v>1</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="10" t="s">
-        <v>426</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>641</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="14"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="14"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="14"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="5" t="s">
-        <v>433</v>
+        <v>650</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>625</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>326</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="G40" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B45" s="5" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B46" s="5" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B48" s="5" t="s">
+        <v>656</v>
       </c>
     </row>
   </sheetData>
@@ -6336,8 +8912,623 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FBFDD87-441C-45E1-A53B-4B23BE47FAEB}">
-  <dimension ref="A1:F1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{898F7DF3-BA9C-4A80-9B8D-BC624C46A485}">
+  <dimension ref="A1:I98"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>670</v>
+      </c>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>673</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>674</v>
+      </c>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>675</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>676</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" s="5"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>685</v>
+      </c>
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="12" t="s">
+        <v>521</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="14"/>
+    </row>
+    <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>680</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="14"/>
+    </row>
+    <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="14"/>
+    </row>
+    <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>684</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="13"/>
+      <c r="I20" s="14"/>
+    </row>
+    <row r="21" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>666</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="I24" s="9" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>692</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>693</v>
+      </c>
+      <c r="D41" s="13"/>
+      <c r="E41" s="14"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>695</v>
+      </c>
+      <c r="D42" s="13"/>
+      <c r="E42" s="14"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="7" t="s">
+        <v>696</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>697</v>
+      </c>
+      <c r="D43" s="13"/>
+      <c r="E43" s="14"/>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="D44" s="13"/>
+      <c r="E44" s="14"/>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="5" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="5" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="5" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="5" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="2"/>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="5" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="5" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="5" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="7" t="s">
+        <v>713</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="7" t="s">
+        <v>715</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="2"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="5" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="2"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="5" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="5" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="5" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="5" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="5" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="5" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B91" s="5" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="5" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="5" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B94" s="5" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B95" s="5" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="5" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="5" t="s">
+        <v>729</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955B6018-0476-4516-BD4C-417DB24D52A3}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
@@ -6357,6 +9548,426 @@
       <c r="E1" s="5"/>
       <c r="F1" s="6"/>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="5" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="5" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="5" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="5" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="5" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="5" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="5" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="5" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="5" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="5" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="5" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="5" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="5" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="5" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="5" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="5" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="5" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="5" t="s">
+        <v>473</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A07F36-7CB1-432D-87A1-BE5EC2BC13C8}">
+  <sheetPr>
+    <tabColor theme="5" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9" style="5"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="e" cm="1">
+        <f t="array" ref="B17">-chgsp   :NULLを半角スペースに変換します。</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="e" cm="1">
+        <f t="array" ref="B18">-chg     :NULLをユニークコードに変換します。</f>
+        <v>#NAME?</v>
+      </c>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>488</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>

--- a/csvpp_manual/CSVPP_TextFile_Generation_and_Processing.xlsx
+++ b/csvpp_manual/CSVPP_TextFile_Generation_and_Processing.xlsx
@@ -8,25 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\gitwork\csvpp\csvpp_manual\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAB3AF84-2165-456B-8811-2D95F9097460}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{656F43C0-840D-4C24-8120-92A95579FE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-600" yWindow="1650" windowWidth="26205" windowHeight="14415" tabRatio="858" activeTab="7" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
+    <workbookView xWindow="-75" yWindow="690" windowWidth="26205" windowHeight="14415" tabRatio="858" xr2:uid="{FC99C8AF-63B4-410E-82B8-E83A41F43691}"/>
   </bookViews>
   <sheets>
-    <sheet name="テキストファイル生成" sheetId="28" r:id="rId1"/>
-    <sheet name="テキストファイル加工" sheetId="29" r:id="rId2"/>
-    <sheet name="テキストファイル分割" sheetId="31" r:id="rId3"/>
-    <sheet name="テキストファイル連結・分割" sheetId="36" r:id="rId4"/>
-    <sheet name="LOG連結" sheetId="37" r:id="rId5"/>
-    <sheet name="改行コード変換" sheetId="38" r:id="rId6"/>
-    <sheet name="XML変換" sheetId="39" r:id="rId7"/>
-    <sheet name="SJIS-EUC変換" sheetId="40" r:id="rId8"/>
-    <sheet name="NULL変換" sheetId="41" r:id="rId9"/>
-    <sheet name="CSV-TAB変換" sheetId="42" r:id="rId10"/>
-    <sheet name="CSVファイルセル内改行コード変換" sheetId="32" r:id="rId11"/>
-    <sheet name="CSVファイル横マージ" sheetId="33" r:id="rId12"/>
-    <sheet name="CSVファイル項目抽出" sheetId="34" r:id="rId13"/>
-    <sheet name="work" sheetId="30" r:id="rId14"/>
+    <sheet name="目次" sheetId="45" r:id="rId1"/>
+    <sheet name="テキストファイル生成" sheetId="28" r:id="rId2"/>
+    <sheet name="テキストファイル加工" sheetId="29" r:id="rId3"/>
+    <sheet name="テキストファイル分割" sheetId="31" r:id="rId4"/>
+    <sheet name="テキストファイル連結・分割" sheetId="36" r:id="rId5"/>
+    <sheet name="LOG連結" sheetId="37" r:id="rId6"/>
+    <sheet name="改行コード変換" sheetId="38" r:id="rId7"/>
+    <sheet name="XML変換" sheetId="39" r:id="rId8"/>
+    <sheet name="HTML変換" sheetId="44" r:id="rId9"/>
+    <sheet name="SJIS-EUC変換" sheetId="40" r:id="rId10"/>
+    <sheet name="NULL変換" sheetId="41" r:id="rId11"/>
+    <sheet name="CSV-TAB変換" sheetId="42" r:id="rId12"/>
+    <sheet name="CSVファイルセル内改行コード変換" sheetId="32" r:id="rId13"/>
+    <sheet name="CSVファイル横マージ" sheetId="33" r:id="rId14"/>
+    <sheet name="CSVファイル項目抽出" sheetId="34" r:id="rId15"/>
+    <sheet name="CSV-DIFF" sheetId="43" r:id="rId16"/>
+    <sheet name="work" sheetId="30" state="hidden" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,30 +48,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1358" uniqueCount="735">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1801" uniqueCount="1019">
   <si>
     <t>[aa]</t>
   </si>
@@ -1495,30 +1476,6 @@
     <t>標準出力へ結果を出力</t>
   </si>
   <si>
-    <t>-----------------------------------------------</t>
-  </si>
-  <si>
-    <t>１．ソフトの紹介</t>
-  </si>
-  <si>
-    <t>２．使用方法</t>
-  </si>
-  <si>
-    <t>本プログラムはコンソールプログラムです。</t>
-  </si>
-  <si>
-    <t>実行形式は以下の通りです。</t>
-  </si>
-  <si>
-    <t>例は以下の通りです。</t>
-  </si>
-  <si>
-    <t>ファイル名にワイルドカードが使用できます。</t>
-  </si>
-  <si>
-    <t>変換ファイル名はフルパスでお願いします。</t>
-  </si>
-  <si>
     <t>#total_tag,DOC</t>
   </si>
   <si>
@@ -1549,165 +1506,6 @@
     <t>&lt;?xml:stylesheet type="text/xsl" href="aaa.xsl"?&gt;</t>
   </si>
   <si>
-    <t>SJIS-EUC変換プログラム</t>
-  </si>
-  <si>
-    <t>本プログラムはＳＪＩＳコードとＥＵＣコードの相互変換するコンソールプログラムです。</t>
-  </si>
-  <si>
-    <t>eucsjis sjis_euc|euc_sjis 変換ファイル名</t>
-  </si>
-  <si>
-    <t>sjis_eucオプションでSJISからEUCに変換します。この時、改行コードは0x0aに変換します。</t>
-  </si>
-  <si>
-    <t>euc_sjisオプションでEUCからSJISに変換します。この時、改行コードは0x0d,0x0aに変換します。</t>
-  </si>
-  <si>
-    <t>オプションで改行コードを指定する時は</t>
-  </si>
-  <si>
-    <t>sjis_euc_win / euc_sjis_win は改行コードは0x0d,0x0aに変換します。</t>
-  </si>
-  <si>
-    <t>sjis_euc_unix / euc_sjis_unix は改行コードは0x0aに変換します。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eucsjis sjis_euc c:\csv\*.txt </t>
-  </si>
-  <si>
-    <t xml:space="preserve">eucsjis euc_sjis c:\csv\*.txt </t>
-  </si>
-  <si>
-    <t>SJISコードの漢字で外字を使用する時はeucsjis.exeのあるディレクトリにeucsjis.csvファイルを置きます。</t>
-  </si>
-  <si>
-    <t>eucsjis.csvには変換則を記述します。添付のeucsjis.csvファイルは私(作者)が調査しましたSJISコードからEUCコードへの変換則です。</t>
-  </si>
-  <si>
-    <t>フォーマットは</t>
-  </si>
-  <si>
-    <t>#sjis_euc,1文字目のコード,2文字目のコード上限,2文字目のコード下限,1文字目のコード差分,2文字目のコード差分</t>
-  </si>
-  <si>
-    <t>#euc_sjis,1文字目のコード,2文字目のコード上限,2文字目のコード下限,1文字目のコード差分,2文字目のコード差分</t>
-  </si>
-  <si>
-    <t>#sjis_eucはsjisコードからeucコード変換の変換規則</t>
-  </si>
-  <si>
-    <t>#euc_sjisはeucコードからsjisコード変換の変換規則</t>
-  </si>
-  <si>
-    <t>以下は例です。</t>
-  </si>
-  <si>
-    <t>#sjis_euc,250,73,64,2,177</t>
-  </si>
-  <si>
-    <t>#sjis_euc,250,83,74,-77,107</t>
-  </si>
-  <si>
-    <t>eucsjis2 sjis_euc|euc_sjis 変換前ファイル名 変換後ファイル名</t>
-  </si>
-  <si>
-    <t>ファイル名はフルパスでお願いします。</t>
-  </si>
-  <si>
-    <t>また、変換前ファイル名に-を指定すると、標準入力になります。変換後ファイル名に-に指定すると標準出力になります。</t>
-  </si>
-  <si>
-    <t>標準出力の時の改行コードは必ず0x0d,0x0aになりますので注意してください。</t>
-  </si>
-  <si>
-    <t>eucsjis2 sjis_euc c:\csv\in.txt c:\csv\out.txt</t>
-  </si>
-  <si>
-    <t>type c:\csv\in.txt | eucsjis2 euc_sjis - - &gt; c:\csv\out.txt</t>
-  </si>
-  <si>
-    <t>NULL削除/置換プログラム</t>
-  </si>
-  <si>
-    <t>テキストファイル(特にCSVファイル)に混ざっているNULLを削除、または半角スペース、またはユニークコードに</t>
-  </si>
-  <si>
-    <t>変換するプログラムです。</t>
-  </si>
-  <si>
-    <t>nullchg 入力ファイル 出力ファイル [-chgsp] [-chg ユニークコード]  [-buff buffer_size]</t>
-  </si>
-  <si>
-    <t>-buff    :一回の読み書きに要する大きさ(単位はKByte)。通常は指定しませんが、ファイルが大きい時などには大きな値を指定すると有効です。指定しない場合は10KByteになっています。</t>
-  </si>
-  <si>
-    <t>※-chgsp、-chgの両方を指定しないときはNULLは削除されます。</t>
-  </si>
-  <si>
-    <t>nullchg.exe Sheet1.csv Sheet1.csv.del</t>
-  </si>
-  <si>
-    <t>nullchg.exe Sheet1.csv Sheet1.csv.sp -chgsp</t>
-  </si>
-  <si>
-    <t>nullchg.exe Sheet1.csv Sheet1.csv.uniq -chg [[NULL]]</t>
-  </si>
-  <si>
-    <t>TABファイル-&gt;CSVファイル変換プログラム</t>
-  </si>
-  <si>
-    <t>本プログラムはCSVMAKE2用フィルタとして作られています。</t>
-  </si>
-  <si>
-    <t>しかし、単体でも動作します。</t>
-  </si>
-  <si>
-    <t>変換内容はTABファイルをCSVファイルに変換します。</t>
-  </si>
-  <si>
-    <t>tabcsv TABファイル CSVファイル [-buff buffer_size] [-dbl_no_cut]</t>
-  </si>
-  <si>
-    <t>tabcsv c:\csv\bbb.txt c:\csv\ccc.csv</t>
-  </si>
-  <si>
-    <t>CSVMAKE2でフィルタプログラムとして使用する場合の例を以下に示します。</t>
-  </si>
-  <si>
-    <t>csvmake2 d:\aaa.xls -x tabcsv  c:\csv\bbb.txt c:\csv\ccc.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSVファイル-&gt;TABファイル変換プログラム </t>
-  </si>
-  <si>
-    <t>本プログラムはCSVMAKE用フィルタとして作られています。</t>
-  </si>
-  <si>
-    <t>変換内容はCSVファイルをTABファイルに変換します。</t>
-  </si>
-  <si>
-    <t>csvtab CSVファイル TABファイル [-buff buffer_size] [-dbl_no_cut]</t>
-  </si>
-  <si>
-    <t>csvtab c:\csv\bbb.csv c:\csv\ccc.txt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type c:\csv\bbb.csv | csvtab - - &gt; c:\csv\ccc.txt </t>
-  </si>
-  <si>
-    <t>※CSVファイル名を-にすると、標準入力になります。</t>
-  </si>
-  <si>
-    <t>※TABファイル名を-にすると、標準出力になります。</t>
-  </si>
-  <si>
-    <t>CSVMAKEでフィルタプログラムとして使用する場合の例を以下に示します。</t>
-  </si>
-  <si>
-    <t>csvmake d:\aaa.xls c:\csv csvtab txt</t>
-  </si>
-  <si>
     <t>txt_catcut は、テキストファイルを 連結（追記） したり、</t>
   </si>
   <si>
@@ -2400,9 +2198,6 @@
     <t>※ -e オプションを指定すると 変換しない</t>
   </si>
   <si>
-    <t>4．ヘッダファイル</t>
-  </si>
-  <si>
     <t>ヘッダファイルは XML の 1行目・2行目 を記述するためのファイルです。</t>
   </si>
   <si>
@@ -2448,13 +2243,1103 @@
   <si>
     <t>テキストファイル分割(csv_textcut)</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eucsjis</t>
+  </si>
+  <si>
+    <t>sjis_euc</t>
+  </si>
+  <si>
+    <t>euc_sjis</t>
+  </si>
+  <si>
+    <t>eucsjis2</t>
+  </si>
+  <si>
+    <t>c:\csv\in.txt</t>
+  </si>
+  <si>
+    <t>c:\csv\out.txt</t>
+  </si>
+  <si>
+    <t>SJIS-EUC変換（eucsjis / eucsjis2）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>eucsjis および eucsjis2 は、</t>
+  </si>
+  <si>
+    <t>Shift-JIS（SJIS） ⇔　EUC-JP（EUC） の相互変換を行うコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>・SJIS → EUC、EUC → SJIS の双方向変換</t>
+  </si>
+  <si>
+    <t>・改行コードの自動変換</t>
+  </si>
+  <si>
+    <t>・外字（ユーザー定義文字）変換規則ファイル（eucsjis.csv）に対応</t>
+  </si>
+  <si>
+    <t>・標準入力／標準出力に対応（eucsjis2）</t>
+  </si>
+  <si>
+    <t>2．eucsjis（複数ファイル変換）</t>
+  </si>
+  <si>
+    <t>sjis_euc|euc_sjis</t>
+  </si>
+  <si>
+    <t>変換前ファイル名</t>
+  </si>
+  <si>
+    <t>変換後ファイル名</t>
+  </si>
+  <si>
+    <t>ファイル名はフルパスで指定</t>
+  </si>
+  <si>
+    <t>ファイル名はフルパスで指定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ワイルドカード（*.txt）使用可能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●変換モード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>モード</t>
+  </si>
+  <si>
+    <t>SJIS → EUC に変換。改行コードは LF (0x0a) に変換</t>
+  </si>
+  <si>
+    <t>EUC → SJIS に変換。改行コードは CRLF (0x0d,0x0a) に変換</t>
+  </si>
+  <si>
+    <t>●改行コード指定オプション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sjis_euc_win / euc_sjis_win</t>
+  </si>
+  <si>
+    <t>CRLF (0x0d,0x0a)</t>
+  </si>
+  <si>
+    <t>sjis_euc_unix / euc_sjis_unix</t>
+  </si>
+  <si>
+    <t>LF (0x0a)</t>
+  </si>
+  <si>
+    <t>3．eucsjis2（単一ファイル変換）</t>
+  </si>
+  <si>
+    <t>●標準入出力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>指定</t>
+  </si>
+  <si>
+    <t>動作</t>
+  </si>
+  <si>
+    <t>変換前ファイル名に -</t>
+  </si>
+  <si>
+    <t>標準入力</t>
+  </si>
+  <si>
+    <t>変換後ファイル名に -</t>
+  </si>
+  <si>
+    <t>標準出力（改行コードは必ず CRLF）</t>
+  </si>
+  <si>
+    <t>標準入力 → 標準出力：</t>
+  </si>
+  <si>
+    <t>SJIS の外字（ユーザー定義文字）を使用する場合は、</t>
+  </si>
+  <si>
+    <t>eucsjis.exe と同じディレクトリに eucsjis.csv を置く必要があります。</t>
+  </si>
+  <si>
+    <t>●フォーマット</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>#sjis_euc,1文字目コード,2文字目コード上限,2文字目コード下限,1文字目差分,2文字目差分</t>
+  </si>
+  <si>
+    <t>#euc_sjis,1文字目コード,2文字目コード上限,2文字目コード下限,1文字目差分,2文字目差分</t>
+  </si>
+  <si>
+    <t>●意味</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>設定名</t>
+  </si>
+  <si>
+    <t>#sjis_euc</t>
+  </si>
+  <si>
+    <t>SJIS → EUC の変換規則</t>
+  </si>
+  <si>
+    <t>#euc_sjis</t>
+  </si>
+  <si>
+    <t>EUC → SJIS の変換規則</t>
+  </si>
+  <si>
+    <t>6．ヘッダファイル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4．外字変換（eucsjis.csv）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>このファイルには SJIS ⇔ EUC の変換規則 を記述します。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　複数ファイルを SJIS⇔EUC に変換</t>
+  </si>
+  <si>
+    <t>　改行コードはモードに応じて自動変換</t>
+  </si>
+  <si>
+    <t>　単一ファイル変換</t>
+  </si>
+  <si>
+    <t>　改行コードは標準出力時 CRLF 固定</t>
+  </si>
+  <si>
+    <t>外字対応（eucsjis.csv）</t>
+  </si>
+  <si>
+    <t>　SJIS 外字を正しく変換するための規則ファイル</t>
+  </si>
+  <si>
+    <t>　SJIS⇔EUC の差分計算を記述可能</t>
+  </si>
+  <si>
+    <t>SJIS と EUC の変換は、古いシステムやログ解析、外部システム連携で今も必要になる場面が多く、</t>
+  </si>
+  <si>
+    <t>このツールは CSVPP の周辺ユーティリティとして非常に重要です。</t>
+  </si>
+  <si>
+    <t>nullchg</t>
+  </si>
+  <si>
+    <t>[-chgsp]</t>
+  </si>
+  <si>
+    <t>[-chg ユニークコード]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>nullchg.exe</t>
+  </si>
+  <si>
+    <t>Sheet1.csv</t>
+  </si>
+  <si>
+    <t>Sheet1.csv.del</t>
+  </si>
+  <si>
+    <t>Sheet1.csv.sp</t>
+  </si>
+  <si>
+    <t>Sheet1.csv.uniq</t>
+  </si>
+  <si>
+    <t>[[NULL]]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -chgsp</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -chg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NULL削除／置換（nullchg）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>nullchg は CSV やテキストファイル内の NULL（空セル）を削除・スペース化・任意文字列へ置換するコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>・NULL を 削除</t>
+  </si>
+  <si>
+    <t>・NULL を 半角スペースへ置換</t>
+  </si>
+  <si>
+    <t>・NULL を 任意のユニークコードへ置換</t>
+  </si>
+  <si>
+    <t>-chgsp</t>
+  </si>
+  <si>
+    <t>NULL を半角スペースに変換</t>
+  </si>
+  <si>
+    <t>-chg ユニークコード</t>
+  </si>
+  <si>
+    <t>NULL を指定した文字列に変換</t>
+  </si>
+  <si>
+    <t>●NULL の扱い</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オプション指定</t>
+  </si>
+  <si>
+    <t>なし</t>
+  </si>
+  <si>
+    <t>NULL を削除</t>
+  </si>
+  <si>
+    <t>NULL → 半角スペース " "</t>
+  </si>
+  <si>
+    <t>-chg [[NULL]]</t>
+  </si>
+  <si>
+    <t>NULL → 任意文字列（例：[[NULL]]）</t>
+  </si>
+  <si>
+    <t>●NULL を削除（デフォルト動作）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ NULL がすべて削除されたファイルを出力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●NULL を半角スペースに変換</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ NULL が " " に置換される</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●NULL をユニークコードに変換</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>→ NULL が [[NULL]] に置換される</t>
+  </si>
+  <si>
+    <t>・nullchg は NULL の削除／スペース化／任意文字列置換ができる前処理ツール</t>
+  </si>
+  <si>
+    <t>・デフォルトは NULL削除</t>
+  </si>
+  <si>
+    <t>・-chgsp でスペース化</t>
+  </si>
+  <si>
+    <t>・-chg で任意文字列へ置換</t>
+  </si>
+  <si>
+    <t>tabcsv</t>
+  </si>
+  <si>
+    <t>TABファイル</t>
+  </si>
+  <si>
+    <t>c:\csv\bbb.txt</t>
+  </si>
+  <si>
+    <t>c:\csv\ccc.csv</t>
+  </si>
+  <si>
+    <t>csvtab</t>
+  </si>
+  <si>
+    <t>c:\csv\bbb.csv</t>
+  </si>
+  <si>
+    <t>c:\csv\ccc.txt</t>
+  </si>
+  <si>
+    <t>TAB区切りのテキストファイルを CSV形式（カンマ区切り） に変換するコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>読み書きバッファサイズ（KByte）。通常は指定不要（デフォルト：10KB）。大規模ファイルで高速化可能。</t>
+  </si>
+  <si>
+    <t>-dbl_no_cut</t>
+  </si>
+  <si>
+    <t>不要なダブルコーテーションを削除しない。</t>
+  </si>
+  <si>
+    <t>→ bbb.txt（TAB区切り）を ccc.csv（CSV形式）に変換</t>
+  </si>
+  <si>
+    <t>CSV形式（カンマ区切り）を TAB区切りファイル に変換するコンソールプログラムです。</t>
+  </si>
+  <si>
+    <t>●標準入力／標準出力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVファイル名に -</t>
+  </si>
+  <si>
+    <t>TABファイル名に -</t>
+  </si>
+  <si>
+    <t>標準出力</t>
+  </si>
+  <si>
+    <t>CSV → TAB（通常）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSV → TAB（標準入力 → 標準出力）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>・TAB区切りをカンマ区切りへ変換</t>
+  </si>
+  <si>
+    <t>・シェルパイプと組み合わせて柔軟な変換が可能</t>
+  </si>
+  <si>
+    <t>・TAB → CSV の変換ツール</t>
+  </si>
+  <si>
+    <t>・-dbl_no_cut でダブルコーテーションの扱いを制御</t>
+  </si>
+  <si>
+    <t>・-buff で高速化可能</t>
+  </si>
+  <si>
+    <t>・CSV → TAB の変換ツール</t>
+  </si>
+  <si>
+    <t>#key,900,200,300,300,44444444444444444</t>
+  </si>
+  <si>
+    <t>#ggg,200</t>
+  </si>
+  <si>
+    <t>#ggg,300</t>
+  </si>
+  <si>
+    <t>#gkkff,400,333333333333333333333</t>
+  </si>
+  <si>
+    <t>#key,200,300</t>
+  </si>
+  <si>
+    <t>#key,200,3012</t>
+  </si>
+  <si>
+    <t>#key,200,302</t>
+  </si>
+  <si>
+    <t>#gggg</t>
+  </si>
+  <si>
+    <t>#ddd</t>
+  </si>
+  <si>
+    <t>#key,200,303</t>
+  </si>
+  <si>
+    <t>#ffff</t>
+  </si>
+  <si>
+    <t>#key,200,3042</t>
+  </si>
+  <si>
+    <t>#ggg</t>
+  </si>
+  <si>
+    <t>#key,900,200</t>
+  </si>
+  <si>
+    <t>#gkkff,400</t>
+  </si>
+  <si>
+    <t>#fff,990</t>
+  </si>
+  <si>
+    <t>#key,200,301</t>
+  </si>
+  <si>
+    <t>#key,[SKIP]</t>
+  </si>
+  <si>
+    <t>#key,200,304d</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2   |                              | |2   |                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3   |#ggg,200                      | |3   |#ggg,200                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4   |#ggg,300                      | |4   |#ggg,300                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5   |                              | |5   |                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">6   |#gkkff,400,333333333333333333 | |6   |#gkkff,400                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">7   |                              | |7   |                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">8   |#key,200,300                  |o|8   |#key,200,300                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    |                              | |9   |#fff,990                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    |                              | |10  |                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">9   |#key,200,3012                 |x|11  |#key,200,301                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    |                              | |12  |#gggg                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    |                              | |13  |                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">10  |#key,200,302                  |o|14  |#key,200,302                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">11  |#gggg                         | |    |                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">12  |#ddd                          | |    |                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">13  |#key,200,303                  |o|15  |#key,200,303                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14  |#ffff                         | |    |                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15  |#key,200,3042                 |-|16  |#key,[SKIP]                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16  |#ggg                          | |17  |                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    |                              |x|18  |#key,200,304d                 </t>
+  </si>
+  <si>
+    <t>csvdiff</t>
+  </si>
+  <si>
+    <t>チェック文字列</t>
+  </si>
+  <si>
+    <t>ファイル1</t>
+  </si>
+  <si>
+    <t>ファイル2</t>
+  </si>
+  <si>
+    <t>[-d]</t>
+  </si>
+  <si>
+    <t>[-integer]</t>
+  </si>
+  <si>
+    <t>[-m ミスマッチ最大数]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[-w 横の表示文字数]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>[-dbl_no_cut]</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>aaa.csv</t>
+  </si>
+  <si>
+    <t>bbb.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> -dbl_no_cut</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -integer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> -d</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TABファイル ⇔ CSVファイル変換（tabcsv / csvtab）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1．TAB → CSV 変換（tabcsv）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2．CSV → TAB 変換（csvtab）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSVファイル DIFF (セル単位ミスマッチチェック）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>一致／不一致／スキップを判定するコンソールツールです。</t>
+  </si>
+  <si>
+    <t>このプログラムは CSVファイルの特定行（特定キー）だけをセル単位で比較し、</t>
+  </si>
+  <si>
+    <t>・特定キー（例：#key）の行だけ比較対象にする</t>
+  </si>
+  <si>
+    <t>・セル単位で 一致：o / 不一致：x / スキップ：- を表示</t>
+  </si>
+  <si>
+    <t>・比較対象外の行は 空白表示</t>
+  </si>
+  <si>
+    <t>・[SKIP] があるセルは比較をスキップ（-）</t>
+  </si>
+  <si>
+    <t>・数値比較モード（-integer）では</t>
+  </si>
+  <si>
+    <t>　・前ゼロ</t>
+  </si>
+  <si>
+    <t>　・16進数（0x）</t>
+  </si>
+  <si>
+    <t>　・負数</t>
+  </si>
+  <si>
+    <t>　　を正しく比較できる</t>
+  </si>
+  <si>
+    <t>・ミスマッチ数の上限指定（-m）</t>
+  </si>
+  <si>
+    <t>・横幅指定（-w）</t>
+  </si>
+  <si>
+    <t>・詳細表示（-d）</t>
+  </si>
+  <si>
+    <t>・ダブルコーテーションの扱いを制御（-dbl_no_cut）</t>
+  </si>
+  <si>
+    <t>2．比較例（動作イメージ）</t>
+  </si>
+  <si>
+    <t>比較対象キー：#key</t>
+  </si>
+  <si>
+    <t>以下の2つの CSV を比較するとします。</t>
+  </si>
+  <si>
+    <t>●aaa.csv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●bbb.csv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●DIFF結果</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1   |#key,900,200,300,300,44444444 |x|1   |#key,900,200</t>
+  </si>
+  <si>
+    <t>●判定記号の意味</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>記号</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>一致</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>不一致</t>
+  </si>
+  <si>
+    <t>スキップ（[SKIP] がある場合）</t>
+  </si>
+  <si>
+    <t>空白</t>
+  </si>
+  <si>
+    <t>比較対象外の行</t>
+  </si>
+  <si>
+    <t>3．使用方法</t>
+  </si>
+  <si>
+    <t>比較対象となるキー（例：#key）</t>
+  </si>
+  <si>
+    <t>ファイル1, ファイル2</t>
+  </si>
+  <si>
+    <t>比較対象の CSV ファイル</t>
+  </si>
+  <si>
+    <t>-m 数</t>
+  </si>
+  <si>
+    <t>ミスマッチ数の上限。指定数を超えると比較停止。 0 を指定すると全件比較。 デフォルト：20</t>
+  </si>
+  <si>
+    <t>-w 横幅</t>
+  </si>
+  <si>
+    <t>表示横幅（デフォルト：30）</t>
+  </si>
+  <si>
+    <t>-d</t>
+  </si>
+  <si>
+    <t>詳細表示モード</t>
+  </si>
+  <si>
+    <t>ダブルコーテーションを削除しない</t>
+  </si>
+  <si>
+    <t>-integer</t>
+  </si>
+  <si>
+    <t>数値として比較する（前ゼロ・16進数・負数対応）</t>
+  </si>
+  <si>
+    <t>●数値比較モード（-integer）の例</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>19 |#key,0xc8,-500                |o|20 |#key,200,-000500</t>
+  </si>
+  <si>
+    <t>21 |#key,0000200,144              |o|22 |#key,200,0x000090</t>
+  </si>
+  <si>
+    <t>　0xc8 → 200</t>
+  </si>
+  <si>
+    <t>　-000500 → -500</t>
+  </si>
+  <si>
+    <t>　0000200 → 200</t>
+  </si>
+  <si>
+    <t>　0x000090 → 144</t>
+  </si>
+  <si>
+    <t>数値として正しく比較されるため 一致（o） となる。</t>
+  </si>
+  <si>
+    <t>・特定キーの行だけ比較する高精度 DIFF ツール</t>
+  </si>
+  <si>
+    <t>・セル単位で一致／不一致／スキップを判定</t>
+  </si>
+  <si>
+    <t>・[SKIP] による比較スキップ機能</t>
+  </si>
+  <si>
+    <t>・数値比較モードで前ゼロ・16進数・負数を正しく判定</t>
+  </si>
+  <si>
+    <t>・ミスマッチ数上限、横幅指定、詳細表示など柔軟なオプション</t>
+  </si>
+  <si>
+    <t>・CSVPP の検証・データチェックに非常に強力</t>
+  </si>
+  <si>
+    <t>CSV ⇔ HTML 変換（csvhtml / htmlcsv）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSV形式で記述された HTML 構造を実際の HTML に変換する csvhtml と、</t>
+  </si>
+  <si>
+    <t>HTML を CSV形式のタグ定義へ変換する htmlcsv をまとめて説明します。</t>
+  </si>
+  <si>
+    <t>両者は 完全に往復可能な構造を持ち、</t>
+  </si>
+  <si>
+    <t>CSVPP の中で HTML を構造化して扱うための重要なユーティリティです。</t>
+  </si>
+  <si>
+    <t>2．CSV → HTML 変換（csvhtml）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●使用方法</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●変換規則（CSV → HTML）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CSV の行は以下の命令で HTML に変換されます。</t>
+  </si>
+  <si>
+    <t>#cmd,&lt;!--AAAAA</t>
+  </si>
+  <si>
+    <t>#cmd,cmd0</t>
+  </si>
+  <si>
+    <t>#cmd,cmd1</t>
+  </si>
+  <si>
+    <t>#cmd,cmd2</t>
+  </si>
+  <si>
+    <t>#cmd,//--&gt;</t>
+  </si>
+  <si>
+    <t>(1) コメントブロック：#cmd</t>
+  </si>
+  <si>
+    <t>CSV</t>
+  </si>
+  <si>
+    <t>CSV</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HTML</t>
+  </si>
+  <si>
+    <t>&lt;!--AAAAA</t>
+  </si>
+  <si>
+    <t>cmd0</t>
+  </si>
+  <si>
+    <t>cmd1</t>
+  </si>
+  <si>
+    <t>cmd2</t>
+  </si>
+  <si>
+    <t>//--&gt;</t>
+  </si>
+  <si>
+    <t>(2) タグ連結：#tag</t>
+  </si>
+  <si>
+    <t>#tag,HTML</t>
+  </si>
+  <si>
+    <t>#tag,HEAD</t>
+  </si>
+  <si>
+    <t>&lt;HTML&gt;&lt;HEAD&gt;</t>
+  </si>
+  <si>
+    <t>(3) タグ＋属性：#tag</t>
+  </si>
+  <si>
+    <t>#tag,META,name,"GENERATOR"</t>
+  </si>
+  <si>
+    <t>#tag,META,content,"xxx WebSphere XXXXpage Builder V6.0.0 for Windows"</t>
+  </si>
+  <si>
+    <t>&lt;META name="GENERATOR" content="xxx WebSphere XXXXpage Builder V6.0.0 for Windows"&gt;</t>
+  </si>
+  <si>
+    <t>(4) DOCTYPE：複数行 → 1行</t>
+  </si>
+  <si>
+    <t>#tag,!DOCTYPE,HTML</t>
+  </si>
+  <si>
+    <t>#tag,!DOCTYPE,PUBLIC</t>
+  </si>
+  <si>
+    <t>#tag,!DOCTYPE,"-//W3C//DTD HTML 4.01 Transitional//EN"</t>
+  </si>
+  <si>
+    <t>&lt;!DOCTYPE HTML PUBLIC "-//W3C//DTD HTML 4.01 Transitional//EN"&gt;</t>
+  </si>
+  <si>
+    <t>(5) 複雑なタグ構造（入れ子＋テキスト）</t>
+  </si>
+  <si>
+    <t>#tag,TD,width,"645"</t>
+  </si>
+  <si>
+    <t>#tag,B</t>
+  </si>
+  <si>
+    <t>#tag,FONT,face,"ＭＳ ゴシック"</t>
+  </si>
+  <si>
+    <t>#wr,CSV</t>
+  </si>
+  <si>
+    <t>#tag,/FONT</t>
+  </si>
+  <si>
+    <t>#wr,ファイル→Verilog-HDL（ＲＴＬ） 変換プログラム</t>
+  </si>
+  <si>
+    <t>#wr,Ver1.00</t>
+  </si>
+  <si>
+    <t>#tag,A,href,"csvvrtl100.lzh"</t>
+  </si>
+  <si>
+    <t>#wr,csvvrtｌ100.LZH (148KB)</t>
+  </si>
+  <si>
+    <t>#tag,/A</t>
+  </si>
+  <si>
+    <t>#tag,/B</t>
+  </si>
+  <si>
+    <t>#tag,/TD</t>
+  </si>
+  <si>
+    <t>&lt;TD width="645"&gt;&lt;B&gt;&lt;FONT face="ＭＳ ゴシック"&gt;CSV&lt;/FONT&gt;ファイル→Verilog-HDL（ＲＴＬ） 変換プログラム &lt;FONT face="ＭＳ ゴシック"&gt;Ver1.00&lt;/FONT&gt; &lt;A href="csvvrtl100.lzh"&gt;csvvrtｌ100.LZH (148KB)&lt;/A&gt;&lt;/B&gt;&lt;/TD&gt;</t>
+  </si>
+  <si>
+    <t>(6) タグ連続：#tagchg</t>
+  </si>
+  <si>
+    <t>#tag,BR</t>
+  </si>
+  <si>
+    <t>#tagchg</t>
+  </si>
+  <si>
+    <t>&lt;BR&gt;&lt;BR&gt;</t>
+  </si>
+  <si>
+    <t>(7) 改行制御：#rc_mode / #rcode</t>
+  </si>
+  <si>
+    <t>#rc_mode</t>
+  </si>
+  <si>
+    <t>#tag,!doctype,html</t>
+  </si>
+  <si>
+    <t>#tag,!doctype,public</t>
+  </si>
+  <si>
+    <t>#tag,!doctype,"-//w3c//dtd html 4.0 transitional//EN"</t>
+  </si>
+  <si>
+    <t>#rcode</t>
+  </si>
+  <si>
+    <t>#tag,html,lang,"ja"</t>
+  </si>
+  <si>
+    <t>#tag,head</t>
+  </si>
+  <si>
+    <t>&lt;!doctype html public "-//w3c//dtd html 4.0 transitional//EN"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;html lang="ja"&gt;</t>
+  </si>
+  <si>
+    <t>&lt;head&gt;</t>
+  </si>
+  <si>
+    <t>3．HTML → CSV 変換プログラム（htmlcsv）</t>
+  </si>
+  <si>
+    <t>●-r オプション</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>タグ内の改行は無視</t>
+  </si>
+  <si>
+    <t>#rc_mode と #rcode を使った CSV が生成される</t>
+  </si>
+  <si>
+    <t>HTML の改行を CSV に反映する</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●変換規則（HTML → CSV）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>csvhtml の逆変換です。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4．まとめ（往復可能な変換体系）</t>
+  </si>
+  <si>
+    <t>方向</t>
+  </si>
+  <si>
+    <t>プログラム</t>
+  </si>
+  <si>
+    <t>主な機能</t>
+  </si>
+  <si>
+    <t>CSV → HTML</t>
+  </si>
+  <si>
+    <t>csvhtml</t>
+  </si>
+  <si>
+    <t>タグ生成、属性生成、テキスト挿入、改行制御</t>
+  </si>
+  <si>
+    <t>HTML → CSV</t>
+  </si>
+  <si>
+    <t>htmlcsv</t>
+  </si>
+  <si>
+    <t>HTMLを構造化CSVへ変換、改行反映（-r）</t>
+  </si>
+  <si>
+    <t>・両者は完全に往復可能</t>
+  </si>
+  <si>
+    <t>・CSVでHTMLを構造化して扱える</t>
+  </si>
+  <si>
+    <t>・HTMLをCSVに戻して再編集できる</t>
+  </si>
+  <si>
+    <t>CSVファイル名</t>
+  </si>
+  <si>
+    <t>HTMLファイル名</t>
+  </si>
+  <si>
+    <t>c:\csv\in.csv</t>
+  </si>
+  <si>
+    <t>c:\csv\out.html</t>
+  </si>
+  <si>
+    <t>[-r]</t>
+  </si>
+  <si>
+    <t>c:\csv\in.html</t>
+  </si>
+  <si>
+    <t>-r</t>
+  </si>
+  <si>
+    <t>目次</t>
+    <rPh sb="0" eb="2">
+      <t>モクジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストファイル生成</t>
+  </si>
+  <si>
+    <t>テキストファイル加工</t>
+  </si>
+  <si>
+    <t>テキストファイル分割</t>
+  </si>
+  <si>
+    <t>テキストファイル連結・分割</t>
+  </si>
+  <si>
+    <t>LOG連結</t>
+  </si>
+  <si>
+    <t>改行コード変換</t>
+  </si>
+  <si>
+    <t>XML変換</t>
+  </si>
+  <si>
+    <t>HTML変換</t>
+  </si>
+  <si>
+    <t>SJIS-EUC変換</t>
+  </si>
+  <si>
+    <t>NULL変換</t>
+  </si>
+  <si>
+    <t>CSV-TAB変換</t>
+  </si>
+  <si>
+    <t>CSVファイルセル内改行コード変換</t>
+  </si>
+  <si>
+    <t>CSVファイル横マージ</t>
+  </si>
+  <si>
+    <t>CSVファイル項目抽出</t>
+  </si>
+  <si>
+    <t>CSV-DIFF</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2501,6 +3386,12 @@
       <sz val="11"/>
       <color indexed="12"/>
       <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="ＭＳ ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -2587,7 +3478,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2619,6 +3510,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -2993,22 +3887,121 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C12DC13-CCC4-4651-A1B3-F12AA9B8F770}">
-  <dimension ref="A1:L255"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEAF81AA-3A74-488A-A7AC-CCEB16078C41}">
+  <dimension ref="A1:B17"/>
+  <sheetFormatPr defaultColWidth="4.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="4.5" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955B6018-0476-4516-BD4C-417DB24D52A3}">
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="30.5" style="5" customWidth="1"/>
     <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
-    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="17.875" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="9" style="5"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="15.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>679</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3018,1656 +4011,471 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>269</v>
+        <v>370</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>72</v>
+      <c r="B4" s="5" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>681</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>73</v>
+        <v>609</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>74</v>
+        <v>682</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>75</v>
+        <v>683</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="7"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-    </row>
-    <row r="17" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="6"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B18" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="7"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B19" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B21" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B22" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B23" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B24" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-    </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-    </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B27" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B28" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D28" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B29" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D30" s="7">
-        <v>4</v>
-      </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B31" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D31" s="7">
-        <v>5</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
-      <c r="J31" s="5"/>
-      <c r="K31" s="5"/>
-      <c r="L31" s="5"/>
-    </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B32" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D32" s="7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D33" s="7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B37" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-      <c r="B43" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B45" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D45" s="7"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B46" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D46" s="7"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B48" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D48" s="7"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B49" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D49" s="7"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B50" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D50" s="7"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B52" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" s="7"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B53" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D53" s="7"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B54" s="7"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D55" s="7"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B56" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D56" s="7"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B57" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B58" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="7"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B59" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D59" s="7"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B60" s="7"/>
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B61" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="6" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" s="5"/>
-      <c r="B65" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B67" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B68" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B69" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B71" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B72" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B74" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B77" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B78" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B79" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B81" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B82" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B84" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B87" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B88" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B89" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B90" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B92" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B93" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B94" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B97" s="6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B98" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B100" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B101" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B102" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B103" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B104" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E104" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B105" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E105" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B107" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B108" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C108" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D108" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B109" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D109" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B110" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D110" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B111" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D111" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B112" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C112" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D112" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B113" s="7"/>
-      <c r="C113" s="7"/>
-      <c r="D113" s="7"/>
-    </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B114" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D114" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B115" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D115" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B116" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B117" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D117" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B118" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B120" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B121" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B122" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B123" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B124" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B125" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B126" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B128" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B129" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B130" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C130" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D130" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B132" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B133" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D133" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B135" s="5" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B137" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B138" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C138" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D138" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B139" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C139" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D139" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B143" s="5" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B144" s="5" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B146" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B147" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B149" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B150" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B151" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B152" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B153" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B154" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B156" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B157" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B158" s="5">
-        <v>234567</v>
-      </c>
-    </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B160" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B161" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B162" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B163" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B164" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B165" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B166" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B167" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B168" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B169" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A171" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B172" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B173" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B175" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B176" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B178" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B179" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B180" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B182" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B183" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B184" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B185" s="5" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B186" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B187" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B192" s="5" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B193" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B195" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B196" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B197" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B198" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B199" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B200" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B202" s="5" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B203" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B204" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B205" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B206" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B207" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B208" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B209" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B210" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B211" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B212" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B214" s="5" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B215" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B216" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B217" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B218" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B219" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B220" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B221" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B222" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B223" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="224" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B224" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B226" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B227" s="5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B228" s="5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B229" s="5" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B230" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B231" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B232" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B233" s="5">
-        <v>234567</v>
-      </c>
-    </row>
-    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B234" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B235" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B236" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B237" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B238" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B239" s="5" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B240" s="5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B241" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B242" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A245" s="3" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B246" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B247" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B248" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B249" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B250" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B251" s="5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B252" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B254" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B255" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE2CDF9-050B-4574-9296-ED6789081A87}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
-    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="9" style="5"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>492</v>
+        <v>684</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>685</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>440</v>
+        <v>615</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="e" cm="1">
-        <f t="array" ref="B18">-dbl_no_cut :不要なダブルコーテーションを削除しない様にする。</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="5" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B35" s="5" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="5" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>694</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="14"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>695</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>696</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="14"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>699</v>
+      </c>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="14"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>701</v>
+      </c>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="14"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>687</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>688</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="5" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B44" s="5" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" s="5" t="e" cm="1">
-        <f t="array" ref="B45">-dbl_no_cut :不要なダブルコーテーションを削除しない様にする。</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B48" s="5" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>705</v>
+      </c>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="14"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>707</v>
+      </c>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="14"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="7" t="s">
+        <v>708</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>709</v>
+      </c>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="14"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B49" s="5" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="5" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B52" s="5" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="5" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="5" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" s="5" t="s">
-        <v>272</v>
+        <v>710</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B53" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>677</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="H53" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="I53" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="J53" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="K53" s="9" t="s">
+        <v>678</v>
+      </c>
+      <c r="L53" s="9"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B57" s="5" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B58" s="5" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G59" s="5"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B60" s="5" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B62" s="5" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B63" s="5" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B64" s="5" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B66" s="5" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B67" s="7" t="s">
+        <v>717</v>
+      </c>
+      <c r="C67" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" s="13"/>
+      <c r="E67" s="13"/>
+      <c r="F67" s="14"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B68" s="7" t="s">
+        <v>718</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>719</v>
+      </c>
+      <c r="D68" s="13"/>
+      <c r="E68" s="13"/>
+      <c r="F68" s="14"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>721</v>
+      </c>
+      <c r="D69" s="13"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="14"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B73" s="5" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B74" s="5" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B75" s="5" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B76" s="5" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B78" s="5" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B79" s="5" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B80" s="5" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B81" s="5" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="5" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B84" s="5" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B85" s="5" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="5" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="5" t="s">
+        <v>733</v>
       </c>
     </row>
   </sheetData>
@@ -4679,6 +4487,777 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A07F36-7CB1-432D-87A1-BE5EC2BC13C8}">
+  <dimension ref="A1:H44"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B12" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="14"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>751</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>753</v>
+      </c>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="14"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>621</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="14"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>705</v>
+      </c>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="14"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>757</v>
+      </c>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="14"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>758</v>
+      </c>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="14"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>760</v>
+      </c>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="14"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>743</v>
+      </c>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="H36" s="9"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="5" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B43" s="5" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
+        <v>770</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE2CDF9-050B-4574-9296-ED6789081A87}">
+  <dimension ref="A1:J55"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="7.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7" style="2" customWidth="1"/>
+    <col min="10" max="10" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1"/>
+      <c r="B7" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="C9" s="5"/>
+      <c r="D9" s="5"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="14"/>
+    </row>
+    <row r="11" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>779</v>
+      </c>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="14"/>
+    </row>
+    <row r="12" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>781</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="14"/>
+    </row>
+    <row r="13" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>773</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="5" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
+      <c r="I26" s="14"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>779</v>
+      </c>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="13"/>
+      <c r="I27" s="14"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>781</v>
+      </c>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="13"/>
+      <c r="I28" s="14"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>784</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>704</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>705</v>
+      </c>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="14"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>707</v>
+      </c>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="14"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>787</v>
+      </c>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="14"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G38" s="5"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="I40" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="5" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="5" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="5" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="5" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="5" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="5" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="5" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B54" s="5" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="5" t="s">
+        <v>794</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10FDB6C8-7508-4924-9487-D85D20963946}">
   <dimension ref="A1:H72"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5073,7 +5652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0813E8AE-00FC-4AD0-9277-F1CC2F47FD09}">
   <dimension ref="A1:J44"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5311,7 +5890,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{677577AA-84BE-4292-B32A-990BC6D0E602}">
   <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5549,7 +6128,890 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9A77035-A26F-4EAF-A0B6-F84559F8653E}">
+  <dimension ref="A1:L138"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.75" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="20.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="15" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="5" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="5" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="5" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="5" t="s">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="5" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" s="5" t="s">
+        <v>867</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" s="5" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B24" s="5" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B25" s="2"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>871</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="5" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="5" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="5" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="5" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B41" s="5" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="5" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="5" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="44" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B44" s="5" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B45" s="5" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="5" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="5" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="5" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="5" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B50" s="5" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="5" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="5" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B53" s="5" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="5" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="15" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="15" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="15" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B60" s="15" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="15" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="15" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B63" s="15" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B64" s="15" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B65" s="15" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B66" s="15" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B67" s="15" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B68" s="15" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B69" s="15" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="70" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B70" s="15" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B71" s="15" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B72" s="15" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B73" s="15" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B74" s="15" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B75" s="15" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B76" s="15" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B77" s="15" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="79" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B79" s="5" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B80" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="C80" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="D80" s="13"/>
+      <c r="E80" s="13"/>
+      <c r="F80" s="14"/>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B81" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="C81" s="13" t="s">
+        <v>878</v>
+      </c>
+      <c r="D81" s="13"/>
+      <c r="E81" s="13"/>
+      <c r="F81" s="14"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B82" s="7" t="s">
+        <v>879</v>
+      </c>
+      <c r="C82" s="13" t="s">
+        <v>880</v>
+      </c>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="14"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B83" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="C83" s="13" t="s">
+        <v>881</v>
+      </c>
+      <c r="D83" s="13"/>
+      <c r="E83" s="13"/>
+      <c r="F83" s="14"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B84" s="7" t="s">
+        <v>882</v>
+      </c>
+      <c r="C84" s="13" t="s">
+        <v>883</v>
+      </c>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="14"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B88" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="H88" s="9" t="s">
+        <v>842</v>
+      </c>
+      <c r="I88" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="J88" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="K88" s="9" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B90" s="5" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B91" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="D91" s="13"/>
+      <c r="E91" s="13"/>
+      <c r="F91" s="13"/>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
+      <c r="I91" s="14"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B92" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>885</v>
+      </c>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
+      <c r="I92" s="14"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B93" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>887</v>
+      </c>
+      <c r="D93" s="13"/>
+      <c r="E93" s="13"/>
+      <c r="F93" s="13"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="14"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B94" s="7" t="s">
+        <v>888</v>
+      </c>
+      <c r="C94" s="13" t="s">
+        <v>889</v>
+      </c>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="14"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B95" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="C95" s="13" t="s">
+        <v>891</v>
+      </c>
+      <c r="D95" s="13"/>
+      <c r="E95" s="13"/>
+      <c r="F95" s="13"/>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
+      <c r="I95" s="14"/>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B96" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="C96" s="13" t="s">
+        <v>893</v>
+      </c>
+      <c r="D96" s="13"/>
+      <c r="E96" s="13"/>
+      <c r="F96" s="13"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
+      <c r="I96" s="14"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B97" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="C97" s="13" t="s">
+        <v>894</v>
+      </c>
+      <c r="D97" s="13"/>
+      <c r="E97" s="13"/>
+      <c r="F97" s="13"/>
+      <c r="G97" s="13"/>
+      <c r="H97" s="13"/>
+      <c r="I97" s="14"/>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B98" s="7" t="s">
+        <v>895</v>
+      </c>
+      <c r="C98" s="13" t="s">
+        <v>896</v>
+      </c>
+      <c r="D98" s="13"/>
+      <c r="E98" s="13"/>
+      <c r="F98" s="13"/>
+      <c r="G98" s="13"/>
+      <c r="H98" s="13"/>
+      <c r="I98" s="14"/>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B100" s="5" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B102" s="15" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B103" s="15" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B105" s="15" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B106" s="15" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B107" s="15" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B108" s="15" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B109" s="5" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B112" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="G112" s="7"/>
+      <c r="H112" s="7"/>
+      <c r="I112" s="7"/>
+      <c r="J112" s="7"/>
+      <c r="K112" s="7"/>
+      <c r="L112" s="7"/>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B113" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E113" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="G113" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="H113" s="7">
+        <v>2</v>
+      </c>
+      <c r="I113" s="7"/>
+      <c r="J113" s="7"/>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7"/>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B114" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E114" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="G114" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="H114" s="7">
+        <v>80</v>
+      </c>
+      <c r="I114" s="7"/>
+      <c r="J114" s="7"/>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7"/>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B115" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E115" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="G115" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="H115" s="7">
+        <v>80</v>
+      </c>
+      <c r="I115" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="J115" s="7">
+        <v>0</v>
+      </c>
+      <c r="K115" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="L115" s="7"/>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B116" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="E116" s="7">
+        <v>80</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="G116" s="7">
+        <v>0</v>
+      </c>
+      <c r="H116" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="I116" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J116" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="K116" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="L116" s="7"/>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B117" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="F117" s="7">
+        <v>80</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="H117" s="7">
+        <v>0</v>
+      </c>
+      <c r="I117" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="J117" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K117" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="L117" s="7" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B118" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="E118" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>844</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="H118" s="7"/>
+      <c r="I118" s="7"/>
+      <c r="J118" s="7"/>
+      <c r="K118" s="7"/>
+      <c r="L118" s="7"/>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A121" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B122" s="5" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B123" s="5" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B124" s="5" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B125" s="5" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B126" s="5" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="B127" s="5" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="138" spans="7:7" x14ac:dyDescent="0.25">
+      <c r="G138" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FBFDD87-441C-45E1-A53B-4B23BE47FAEB}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -5580,6 +7042,1477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C12DC13-CCC4-4651-A1B3-F12AA9B8F770}">
+  <dimension ref="A1:L255"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
+    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
+    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9" style="5"/>
+    <col min="7" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B19" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B23" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B24" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+    </row>
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+    </row>
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B27" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D28" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D30" s="7">
+        <v>4</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B31" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" s="7">
+        <v>5</v>
+      </c>
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="5"/>
+      <c r="L31" s="5"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B32" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D32" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D33" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="4"/>
+      <c r="B43" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="7"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" s="7"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D46" s="7"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D48" s="7"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D49" s="7"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D50" s="7"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="7"/>
+      <c r="C51" s="7"/>
+      <c r="D51" s="7"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D52" s="7"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D53" s="7"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="7"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D55" s="7"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B56" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D56" s="7"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D57" s="7"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B58" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="7"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B59" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="7"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B60" s="7"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B61" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="6" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="5"/>
+      <c r="B65" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B81" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B82" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B84" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B87" s="6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B88" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B89" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B90" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B92" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B93" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B94" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B97" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B98" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B100" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B101" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B102" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B103" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B104" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B105" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B107" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B108" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C108" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D108" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B109" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D109" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B110" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C110" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B111" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D111" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B112" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C112" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D112" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B113" s="7"/>
+      <c r="C113" s="7"/>
+      <c r="D113" s="7"/>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B114" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C114" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D114" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B115" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D115" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B116" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B117" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D117" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B118" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B120" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B121" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B122" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B123" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B124" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B125" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B126" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B128" s="6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B129" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B130" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C130" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D130" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B132" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B133" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B135" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B137" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B138" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C138" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D138" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B139" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C139" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D139" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A142" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B143" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B144" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B146" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B147" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B149" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B150" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B151" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B152" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B153" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B156" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B157" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B158" s="5">
+        <v>234567</v>
+      </c>
+    </row>
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B160" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B161" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B162" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B163" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B164" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B165" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B166" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B167" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B168" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B169" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A171" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B172" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B173" s="5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B175" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B176" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B178" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B179" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B180" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B182" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B183" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B184" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B185" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B186" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B187" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A190" s="3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B192" s="5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="195" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B195" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B196" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="197" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B197" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="198" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B198" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B199" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B200" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="202" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B202" s="5" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="203" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B203" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B204" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="205" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B205" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="206" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B206" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="207" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B207" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="208" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B208" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="209" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B209" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B210" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="211" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B211" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="212" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B212" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="214" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B214" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="215" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B215" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="216" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B216" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="217" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B217" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="218" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B218" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="219" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B219" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="220" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B220" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="221" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B221" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="222" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B222" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="223" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B223" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="224" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B224" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B226" s="5" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B227" s="5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="228" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B228" s="5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B229" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B230" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B231" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="232" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B232" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="233" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B233" s="5">
+        <v>234567</v>
+      </c>
+    </row>
+    <row r="234" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B234" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="235" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B235" s="5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B236" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B237" s="5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B238" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="239" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B239" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="240" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B240" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B241" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B242" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A245" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B246" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B247" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B248" s="5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B249" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B250" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B251" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B252" s="5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B254" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B255" s="5" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD07EFE1-56C1-4F97-9C22-31B32909660F}">
   <dimension ref="A1:H311"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -7302,7 +10235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D83D69E0-543C-4B91-896D-469DD91AB079}">
   <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -7318,7 +10251,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>734</v>
+        <v>672</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -7609,7 +10542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5DCBBDD-5C69-4CD5-80ED-D60C3A6CB84D}">
   <dimension ref="A1:J77"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -7629,7 +10562,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>733</v>
+        <v>671</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -7639,37 +10572,37 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>507</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>508</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>509</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>510</v>
+        <v>449</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>511</v>
+        <v>450</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>512</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>513</v>
+        <v>452</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -7682,25 +10615,25 @@
         <v>387</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>515</v>
+        <v>454</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>516</v>
+        <v>455</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>517</v>
+        <v>456</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>518</v>
+        <v>457</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>519</v>
+        <v>458</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>520</v>
+        <v>459</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>30</v>
@@ -7708,7 +10641,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B15" s="12" t="s">
-        <v>521</v>
+        <v>460</v>
       </c>
       <c r="C15" s="12" t="s">
         <v>184</v>
@@ -7722,10 +10655,10 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B16" s="7" t="s">
-        <v>522</v>
+        <v>461</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>523</v>
+        <v>462</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -7736,10 +10669,10 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17" s="7" t="s">
-        <v>524</v>
+        <v>463</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>525</v>
+        <v>464</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -7750,10 +10683,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B18" s="7" t="s">
-        <v>526</v>
+        <v>465</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>527</v>
+        <v>466</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -7764,10 +10697,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" s="7" t="s">
-        <v>528</v>
+        <v>467</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>529</v>
+        <v>468</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -7778,10 +10711,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B20" s="7" t="s">
-        <v>530</v>
+        <v>469</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>531</v>
+        <v>470</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -7792,32 +10725,32 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
-        <v>532</v>
+        <v>471</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>533</v>
+        <v>472</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>534</v>
+        <v>473</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>535</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
-        <v>536</v>
+        <v>475</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>538</v>
+        <v>477</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -7825,23 +10758,23 @@
         <v>387</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>515</v>
+        <v>454</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>516</v>
+        <v>455</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>537</v>
+        <v>476</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>539</v>
+        <v>478</v>
       </c>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
@@ -7849,26 +10782,26 @@
         <v>387</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>515</v>
+        <v>454</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>516</v>
+        <v>455</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>568</v>
+        <v>507</v>
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>540</v>
+        <v>479</v>
       </c>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>541</v>
+        <v>480</v>
       </c>
     </row>
     <row r="37" spans="2:7" x14ac:dyDescent="0.25">
@@ -7876,16 +10809,16 @@
         <v>387</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>515</v>
+        <v>454</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>516</v>
+        <v>455</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>569</v>
+        <v>508</v>
       </c>
       <c r="G37" s="7">
         <v>100</v>
@@ -7893,12 +10826,12 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
-        <v>542</v>
+        <v>481</v>
       </c>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
-        <v>543</v>
+        <v>482</v>
       </c>
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
@@ -7906,16 +10839,16 @@
         <v>387</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>515</v>
+        <v>454</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>516</v>
+        <v>455</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>570</v>
+        <v>509</v>
       </c>
       <c r="G41" s="7">
         <v>200</v>
@@ -7923,17 +10856,17 @@
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
-        <v>544</v>
+        <v>483</v>
       </c>
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="5" t="s">
-        <v>545</v>
+        <v>484</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
-        <v>546</v>
+        <v>485</v>
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
@@ -7941,16 +10874,16 @@
         <v>387</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>515</v>
+        <v>454</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>516</v>
+        <v>455</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>571</v>
+        <v>510</v>
       </c>
       <c r="G46" s="7">
         <v>100</v>
@@ -7958,17 +10891,17 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
-        <v>547</v>
+        <v>486</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
-        <v>561</v>
+        <v>500</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" s="5" t="s">
-        <v>556</v>
+        <v>495</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -7976,16 +10909,16 @@
         <v>387</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>572</v>
+        <v>511</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>550</v>
+        <v>489</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>568</v>
+        <v>507</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -7993,13 +10926,13 @@
         <v>387</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>551</v>
+        <v>490</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>550</v>
+        <v>489</v>
       </c>
       <c r="F53" s="7"/>
     </row>
@@ -8008,39 +10941,39 @@
         <v>387</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>552</v>
+        <v>491</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>550</v>
+        <v>489</v>
       </c>
       <c r="F54" s="7"/>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B56" s="5" t="s">
-        <v>549</v>
+        <v>488</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B57" s="5" t="s">
-        <v>553</v>
+        <v>492</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B58" s="5" t="s">
-        <v>554</v>
+        <v>493</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B59" s="5" t="s">
-        <v>555</v>
+        <v>494</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" s="5" t="s">
-        <v>557</v>
+        <v>496</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
@@ -8048,19 +10981,19 @@
         <v>387</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>573</v>
+        <v>512</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>574</v>
+        <v>513</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>568</v>
+        <v>507</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>571</v>
+        <v>510</v>
       </c>
       <c r="H62" s="7">
         <v>100</v>
@@ -8073,25 +11006,25 @@
         <v>387</v>
       </c>
       <c r="C63" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="E63" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="D63" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>575</v>
-      </c>
       <c r="F63" s="7" t="s">
-        <v>568</v>
+        <v>507</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>571</v>
+        <v>510</v>
       </c>
       <c r="H63" s="7">
         <v>100</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>569</v>
+        <v>508</v>
       </c>
       <c r="J63" s="7">
         <v>101</v>
@@ -8102,25 +11035,25 @@
         <v>387</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>514</v>
+        <v>453</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>573</v>
+        <v>512</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>576</v>
+        <v>515</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>568</v>
+        <v>507</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>571</v>
+        <v>510</v>
       </c>
       <c r="H64" s="7">
         <v>100</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>569</v>
+        <v>508</v>
       </c>
       <c r="J64" s="7">
         <v>201</v>
@@ -8128,22 +11061,22 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B66" s="5" t="s">
-        <v>549</v>
+        <v>488</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B67" s="5" t="s">
-        <v>558</v>
+        <v>497</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B68" s="5" t="s">
-        <v>559</v>
+        <v>498</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B69" s="5" t="s">
-        <v>560</v>
+        <v>499</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -8153,32 +11086,32 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B72" s="5" t="s">
-        <v>562</v>
+        <v>501</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B73" s="5" t="s">
-        <v>563</v>
+        <v>502</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B74" s="5" t="s">
-        <v>567</v>
+        <v>506</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B75" s="5" t="s">
-        <v>564</v>
+        <v>503</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B76" s="5" t="s">
-        <v>565</v>
+        <v>504</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B77" s="5" t="s">
-        <v>566</v>
+        <v>505</v>
       </c>
     </row>
   </sheetData>
@@ -8189,7 +11122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E5C4333-F641-40BB-B2E3-89805723AF26}">
   <dimension ref="A1:G57"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -8205,7 +11138,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>732</v>
+        <v>670</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8220,41 +11153,41 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>588</v>
+        <v>527</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>589</v>
+        <v>528</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>590</v>
+        <v>529</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>591</v>
+        <v>530</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>592</v>
+        <v>531</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>593</v>
+        <v>532</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>594</v>
+        <v>533</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>595</v>
+        <v>534</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -8267,13 +11200,13 @@
         <v>387</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>578</v>
+        <v>517</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>579</v>
+        <v>518</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
@@ -8283,16 +11216,16 @@
         <v>387</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>586</v>
+        <v>525</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>579</v>
+        <v>518</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>580</v>
+        <v>519</v>
       </c>
       <c r="G14" s="7"/>
     </row>
@@ -8301,29 +11234,29 @@
         <v>387</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>587</v>
+        <v>526</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>579</v>
+        <v>518</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>581</v>
+        <v>520</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>582</v>
+        <v>521</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>596</v>
+        <v>535</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
-        <v>597</v>
+        <v>536</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -8331,20 +11264,20 @@
         <v>387</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>578</v>
+        <v>517</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>579</v>
+        <v>518</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>599</v>
+        <v>538</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
@@ -8353,7 +11286,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>598</v>
+        <v>537</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
@@ -8362,7 +11295,7 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B24" s="2" t="s">
-        <v>600</v>
+        <v>539</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
@@ -8374,22 +11307,22 @@
         <v>387</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>586</v>
+        <v>525</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>579</v>
+        <v>518</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>580</v>
+        <v>519</v>
       </c>
       <c r="G25" s="7"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
-        <v>601</v>
+        <v>540</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -8398,7 +11331,7 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
-        <v>602</v>
+        <v>541</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
@@ -8414,7 +11347,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>603</v>
+        <v>542</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -8422,54 +11355,54 @@
         <v>387</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>587</v>
+        <v>526</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>579</v>
+        <v>518</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>581</v>
+        <v>520</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>582</v>
+        <v>521</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>604</v>
+        <v>543</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
-        <v>605</v>
+        <v>544</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>606</v>
+        <v>545</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
-        <v>607</v>
+        <v>546</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>608</v>
+        <v>547</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>548</v>
+        <v>487</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
-        <v>610</v>
+        <v>549</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
@@ -8477,25 +11410,25 @@
         <v>387</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>583</v>
+        <v>522</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>584</v>
+        <v>523</v>
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B42" s="5" t="s">
-        <v>609</v>
+        <v>548</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B44" s="5" t="s">
-        <v>611</v>
+        <v>550</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -8503,27 +11436,27 @@
         <v>387</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>586</v>
+        <v>525</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>584</v>
+        <v>523</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>585</v>
+        <v>524</v>
       </c>
       <c r="G45" s="7"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B46" s="5" t="s">
-        <v>612</v>
+        <v>551</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B48" s="5" t="s">
-        <v>613</v>
+        <v>552</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
@@ -8531,13 +11464,13 @@
         <v>387</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>577</v>
+        <v>516</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>587</v>
+        <v>526</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>584</v>
+        <v>523</v>
       </c>
       <c r="F49" s="7">
         <v>20000</v>
@@ -8548,7 +11481,7 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B50" s="5" t="s">
-        <v>614</v>
+        <v>553</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -8558,22 +11491,22 @@
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B54" s="5" t="s">
-        <v>615</v>
+        <v>554</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B55" s="5" t="s">
-        <v>616</v>
+        <v>555</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B56" s="5" t="s">
-        <v>617</v>
+        <v>556</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B57" s="5" t="s">
-        <v>618</v>
+        <v>557</v>
       </c>
     </row>
   </sheetData>
@@ -8584,7 +11517,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E8EB3C0-1183-4B92-862F-140ADBEFBE28}">
   <dimension ref="A1:I48"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -8602,7 +11535,7 @@
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>731</v>
+        <v>669</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8617,56 +11550,56 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>628</v>
+        <v>567</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>627</v>
+        <v>566</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="7" t="s">
-        <v>629</v>
+        <v>568</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>630</v>
+        <v>569</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>521</v>
+        <v>460</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B8" s="7" t="s">
-        <v>631</v>
+        <v>570</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>632</v>
+        <v>571</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>633</v>
+        <v>572</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
-        <v>634</v>
+        <v>573</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>635</v>
+        <v>574</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>636</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="7" t="s">
-        <v>637</v>
+        <v>576</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>638</v>
+        <v>577</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>639</v>
+        <v>578</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -8679,10 +11612,10 @@
         <v>387</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>619</v>
+        <v>558</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>620</v>
+        <v>559</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>108</v>
@@ -8693,12 +11626,12 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
-        <v>640</v>
+        <v>579</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B17" s="12" t="s">
-        <v>521</v>
+        <v>460</v>
       </c>
       <c r="C17" s="12" t="s">
         <v>184</v>
@@ -8712,10 +11645,10 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
-        <v>633</v>
+        <v>572</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>641</v>
+        <v>580</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -8726,10 +11659,10 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B19" s="12" t="s">
-        <v>636</v>
+        <v>575</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>642</v>
+        <v>581</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -8740,10 +11673,10 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B20" s="12" t="s">
-        <v>639</v>
+        <v>578</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>643</v>
+        <v>582</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -8754,10 +11687,10 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">
-        <v>530</v>
+        <v>469</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>531</v>
+        <v>470</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
@@ -8768,22 +11701,22 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>644</v>
+        <v>583</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>645</v>
+        <v>584</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>646</v>
+        <v>585</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
-        <v>647</v>
+        <v>586</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
@@ -8793,7 +11726,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>648</v>
+        <v>587</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -8801,18 +11734,18 @@
         <v>387</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>619</v>
+        <v>558</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>623</v>
+        <v>562</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>621</v>
+        <v>560</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>649</v>
+        <v>588</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -8820,18 +11753,18 @@
         <v>387</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>619</v>
+        <v>558</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>624</v>
+        <v>563</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>622</v>
+        <v>561</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>650</v>
+        <v>589</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -8839,10 +11772,10 @@
         <v>387</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>619</v>
+        <v>558</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>625</v>
+        <v>564</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>326</v>
@@ -8850,7 +11783,7 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B39" s="5" t="s">
-        <v>651</v>
+        <v>590</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
@@ -8858,16 +11791,16 @@
         <v>387</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>619</v>
+        <v>558</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>625</v>
+        <v>564</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>326</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>626</v>
+        <v>565</v>
       </c>
       <c r="G40" s="7">
         <v>100</v>
@@ -8880,27 +11813,27 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B44" s="5" t="s">
-        <v>652</v>
+        <v>591</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B45" s="5" t="s">
-        <v>653</v>
+        <v>592</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B46" s="5" t="s">
-        <v>654</v>
+        <v>593</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B47" s="5" t="s">
-        <v>655</v>
+        <v>594</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B48" s="5" t="s">
-        <v>656</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
@@ -8911,7 +11844,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{898F7DF3-BA9C-4A80-9B8D-BC624C46A485}">
   <dimension ref="A1:I98"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
@@ -8930,7 +11863,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>730</v>
+        <v>668</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -8957,7 +11890,7 @@
     </row>
     <row r="4" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
-        <v>671</v>
+        <v>610</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -8966,7 +11899,7 @@
     </row>
     <row r="5" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
-        <v>670</v>
+        <v>609</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -8975,7 +11908,7 @@
     </row>
     <row r="6" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
-        <v>672</v>
+        <v>611</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
@@ -8984,7 +11917,7 @@
     </row>
     <row r="7" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
-        <v>673</v>
+        <v>612</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -8993,7 +11926,7 @@
     </row>
     <row r="8" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
-        <v>674</v>
+        <v>613</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5"/>
@@ -9002,7 +11935,7 @@
     </row>
     <row r="9" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
-        <v>675</v>
+        <v>614</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="5"/>
@@ -9011,7 +11944,7 @@
     </row>
     <row r="10" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
-        <v>676</v>
+        <v>615</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5"/>
@@ -9040,25 +11973,25 @@
         <v>387</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>657</v>
+        <v>596</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>658</v>
+        <v>597</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>659</v>
+        <v>598</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>661</v>
+        <v>600</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>662</v>
+        <v>601</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>663</v>
+        <v>602</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>660</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -9070,7 +12003,7 @@
     </row>
     <row r="15" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
-        <v>685</v>
+        <v>624</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
@@ -9079,7 +12012,7 @@
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="12" t="s">
-        <v>521</v>
+        <v>460</v>
       </c>
       <c r="C16" s="12" t="s">
         <v>184</v>
@@ -9093,10 +12026,10 @@
     </row>
     <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="12" t="s">
-        <v>677</v>
+        <v>616</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>678</v>
+        <v>617</v>
       </c>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -9107,10 +12040,10 @@
     </row>
     <row r="18" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="12" t="s">
-        <v>679</v>
+        <v>618</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>680</v>
+        <v>619</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -9121,10 +12054,10 @@
     </row>
     <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="12" t="s">
-        <v>681</v>
+        <v>620</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>682</v>
+        <v>621</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -9135,10 +12068,10 @@
     </row>
     <row r="20" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="12" t="s">
-        <v>683</v>
+        <v>622</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>684</v>
+        <v>623</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -9164,13 +12097,13 @@
         <v>387</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>657</v>
+        <v>596</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>664</v>
+        <v>603</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>665</v>
+        <v>604</v>
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
@@ -9182,170 +12115,170 @@
         <v>387</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>657</v>
+        <v>596</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>664</v>
+        <v>603</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>665</v>
+        <v>604</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>668</v>
+        <v>607</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>666</v>
+        <v>605</v>
       </c>
       <c r="H24" s="9" t="s">
-        <v>669</v>
+        <v>608</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>667</v>
+        <v>606</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>700</v>
+        <v>639</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
-        <v>686</v>
+        <v>625</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="5" t="s">
-        <v>687</v>
+        <v>626</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B30" s="5" t="s">
-        <v>688</v>
+        <v>627</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
-        <v>689</v>
+        <v>628</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B33" s="5" t="s">
-        <v>690</v>
+        <v>629</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B36" s="5" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B37" s="5" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B40" s="5" t="s">
-        <v>691</v>
+        <v>630</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B41" s="7" t="s">
-        <v>692</v>
+        <v>631</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>693</v>
+        <v>632</v>
       </c>
       <c r="D41" s="13"/>
       <c r="E41" s="14"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B42" s="7" t="s">
-        <v>694</v>
+        <v>633</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>695</v>
+        <v>634</v>
       </c>
       <c r="D42" s="13"/>
       <c r="E42" s="14"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B43" s="7" t="s">
-        <v>696</v>
+        <v>635</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>697</v>
+        <v>636</v>
       </c>
       <c r="D43" s="13"/>
       <c r="E43" s="14"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B44" s="7" t="s">
-        <v>698</v>
+        <v>637</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>699</v>
+        <v>638</v>
       </c>
       <c r="D44" s="13"/>
       <c r="E44" s="14"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>701</v>
+        <v>640</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" s="5" t="s">
-        <v>702</v>
+        <v>641</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" s="5" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" s="5" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" s="5" t="s">
-        <v>704</v>
+        <v>643</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" s="5" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" s="5" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
@@ -9353,48 +12286,48 @@
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" s="5" t="s">
-        <v>705</v>
+        <v>644</v>
       </c>
     </row>
     <row r="62" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B62" s="5" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>703</v>
+        <v>642</v>
       </c>
     </row>
     <row r="64" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B64" s="5" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
-        <v>706</v>
+        <v>645</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B68" s="5" t="s">
-        <v>707</v>
+        <v>646</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B69" s="7" t="s">
-        <v>708</v>
+        <v>647</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>709</v>
+        <v>648</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B70" s="9" t="s">
-        <v>710</v>
+        <v>649</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>711</v>
+        <v>650</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
@@ -9402,31 +12335,31 @@
         <v>381</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>712</v>
+        <v>651</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B72" s="7" t="s">
-        <v>713</v>
+        <v>652</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>714</v>
+        <v>653</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B73" s="7" t="s">
-        <v>715</v>
+        <v>654</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>716</v>
+        <v>655</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B74" s="7" t="s">
-        <v>717</v>
+        <v>656</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>718</v>
+        <v>657</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -9434,7 +12367,7 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B76" s="5" t="s">
-        <v>719</v>
+        <v>658</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -9442,32 +12375,32 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B80" s="5" t="s">
-        <v>721</v>
+        <v>659</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B82" s="5" t="s">
-        <v>722</v>
+        <v>660</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B83" s="5" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B84" s="5" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B86" s="5" t="s">
-        <v>723</v>
+        <v>661</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
@@ -9477,375 +12410,42 @@
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B90" s="5" t="s">
-        <v>724</v>
+        <v>662</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B91" s="5" t="s">
-        <v>725</v>
+        <v>663</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B92" s="5" t="s">
-        <v>674</v>
+        <v>613</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B93" s="5" t="s">
-        <v>726</v>
+        <v>664</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B94" s="5" t="s">
-        <v>655</v>
+        <v>594</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B95" s="5" t="s">
-        <v>727</v>
+        <v>665</v>
       </c>
     </row>
     <row r="97" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B97" s="5" t="s">
-        <v>728</v>
+        <v>666</v>
       </c>
     </row>
     <row r="98" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B98" s="5" t="s">
-        <v>729</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.75" right="0.35" top="1" bottom="1" header="0.51200000000000001" footer="0.51200000000000001"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955B6018-0476-4516-BD4C-417DB24D52A3}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:F87"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
-    <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
-    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="9" style="5"/>
-    <col min="7" max="16384" width="9" style="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" s="5" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="5" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B33" s="5" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B34" s="5" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B36" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B37" s="5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B39" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B40" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B41" s="5" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B45" s="5" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B47" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B49" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="50" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B50" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B51" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="53" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B53" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="54" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B54" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B55" s="5" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B56" s="5" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B57" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B58" s="5" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B59" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="60" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B60" s="5" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B62" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="63" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B63" s="5" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="64" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B64" s="5" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B66" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B67" s="5" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B69" s="5" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B70" s="5" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B71" s="5" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B75" s="5" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B76" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B78" s="5" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B79" s="5" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B80" s="5" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B82" s="5" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B83" s="5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="85" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B85" s="5" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B86" s="5" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B87" s="5" t="s">
-        <v>473</v>
+        <v>667</v>
       </c>
     </row>
   </sheetData>
@@ -9857,24 +12457,23 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7A07F36-7CB1-432D-87A1-BE5EC2BC13C8}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.79998168889431442"/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7874464B-0C5D-4E8D-9991-038A3AC2E5D6}">
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.25" style="3" customWidth="1"/>
     <col min="2" max="2" width="25.625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.25" style="5" customWidth="1"/>
-    <col min="4" max="4" width="38.25" style="5" customWidth="1"/>
-    <col min="5" max="5" width="21.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="9" style="5"/>
+    <col min="3" max="3" width="15.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" style="5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.625" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="3" customFormat="1" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>911</v>
+      </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
       <c r="D1" s="5"/>
@@ -9882,90 +12481,588 @@
       <c r="F1" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
-        <v>480</v>
+      <c r="A3" s="3" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
+        <v>912</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>436</v>
+      <c r="B5" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>914</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>481</v>
+      <c r="B7" t="s">
+        <v>915</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>482</v>
+      <c r="A9" s="3" t="s">
+        <v>916</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
-        <v>438</v>
+        <v>917</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>440</v>
+      <c r="B12" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>988</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>996</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>997</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="5" t="s">
-        <v>484</v>
+        <v>325</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>988</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>998</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>999</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" s="5" t="e" cm="1">
-        <f t="array" ref="B17">-chgsp   :NULLを半角スペースに変換します。</f>
-        <v>#NAME?</v>
+      <c r="B17" s="5" t="s">
+        <v>918</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="e" cm="1">
-        <f t="array" ref="B18">-chg     :NULLをユニークコードに変換します。</f>
-        <v>#NAME?</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" s="5" t="s">
-        <v>485</v>
+      <c r="B18" s="5" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
+        <v>925</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" s="5" t="s">
-        <v>441</v>
+      <c r="B22" s="6" t="s">
+        <v>927</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
-        <v>486</v>
+        <v>920</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
-        <v>487</v>
+        <v>921</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
-        <v>488</v>
+        <v>922</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="5" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="5" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="5" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B33" s="5" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B34" s="5" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B37" s="5" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B39" s="5" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B40" s="5" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B42" s="3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="43" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B43" s="2" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="46" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B46" s="5" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="47" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B47" s="3" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="48" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B48" s="5" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B49" s="5" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="51" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B51" s="3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="52" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B52" s="5" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B55" s="5" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B56" s="3" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B57" s="5" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B58" s="5" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B59" s="5" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B61" s="3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B62" s="5" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="65" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B65" s="5" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B66" s="3" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B67" s="5" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B68" s="5" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B69" s="5" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B70" s="5" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B71" s="5" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B72" s="5" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B73" s="5" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B74" s="5" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B75" s="5" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B76" s="5" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B77" s="5" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="78" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B78" s="5" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="79" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B79" s="5" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="80" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B80" s="5" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B82" s="3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B83" s="5" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B86" s="5" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B87" s="3" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B88" s="5" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B89" s="5" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B90" s="5" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="92" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B92" s="3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="93" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B93" s="5" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="96" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B96" s="5" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="97" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B97" s="3" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="98" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B98" s="5" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="99" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B99" s="5" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="100" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B100" s="5" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="101" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B101" s="5" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="102" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B102" s="5" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="103" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B103" s="5" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="104" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B104" s="5" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="105" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B105" s="5" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="106" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B106" s="5" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="108" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B108" s="3" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="109" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B109" s="5" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="110" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B110" s="5" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="111" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B111" s="5" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="3" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B116" s="5" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B117" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E117" s="7" t="s">
+        <v>997</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B119" s="5" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B120" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="D120" s="7" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="F120" s="7"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B121" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E121" s="7" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B123" s="5" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B124" s="5" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B125" s="5" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B126" s="5" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B128" s="5" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B129" s="5" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A132" s="3" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B133" s="7" t="s">
+        <v>984</v>
+      </c>
+      <c r="C133" s="7" t="s">
+        <v>985</v>
+      </c>
+      <c r="D133" s="7" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B134" s="7" t="s">
+        <v>987</v>
+      </c>
+      <c r="C134" s="7" t="s">
+        <v>988</v>
+      </c>
+      <c r="D134" s="7" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B135" s="7" t="s">
+        <v>990</v>
+      </c>
+      <c r="C135" s="7" t="s">
+        <v>991</v>
+      </c>
+      <c r="D135" s="7" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B137" s="5" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B138" s="5" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B139" s="5" t="s">
+        <v>995</v>
       </c>
     </row>
   </sheetData>
